--- a/pds_admin_tamilnadu/Backend/Backend/Data_2.xlsx
+++ b/pds_admin_tamilnadu/Backend/Backend/Data_2.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1016" uniqueCount="732">
   <si>
     <t>SW_ID</t>
   </si>
@@ -41,18 +41,1572 @@
     <t>Demand_Wheat</t>
   </si>
   <si>
+    <t>A61</t>
+  </si>
+  <si>
+    <t>A62</t>
+  </si>
+  <si>
+    <t>A63</t>
+  </si>
+  <si>
+    <t>A64</t>
+  </si>
+  <si>
+    <t>A65</t>
+  </si>
+  <si>
+    <t>A66</t>
+  </si>
+  <si>
+    <t>A67</t>
+  </si>
+  <si>
+    <t>A68</t>
+  </si>
+  <si>
+    <t>A69</t>
+  </si>
+  <si>
+    <t>A70</t>
+  </si>
+  <si>
+    <t>A72</t>
+  </si>
+  <si>
+    <t>A73</t>
+  </si>
+  <si>
+    <t>A74</t>
+  </si>
+  <si>
+    <t>A75</t>
+  </si>
+  <si>
+    <t>A76</t>
+  </si>
+  <si>
+    <t>A77</t>
+  </si>
+  <si>
+    <t>A79</t>
+  </si>
+  <si>
+    <t>A80</t>
+  </si>
+  <si>
+    <t>A83</t>
+  </si>
+  <si>
+    <t>A96</t>
+  </si>
+  <si>
+    <t>B14</t>
+  </si>
+  <si>
+    <t>B15</t>
+  </si>
+  <si>
+    <t>B22</t>
+  </si>
+  <si>
+    <t>B65</t>
+  </si>
+  <si>
+    <t>B88</t>
+  </si>
+  <si>
+    <t>B95</t>
+  </si>
+  <si>
+    <t>C09</t>
+  </si>
+  <si>
+    <t>C10</t>
+  </si>
+  <si>
+    <t>C11</t>
+  </si>
+  <si>
+    <t>C12</t>
+  </si>
+  <si>
+    <t>C16</t>
+  </si>
+  <si>
+    <t>C26</t>
+  </si>
+  <si>
+    <t>C90</t>
+  </si>
+  <si>
+    <t>Gopalapuram</t>
+  </si>
+  <si>
+    <t>Bathlagundu</t>
+  </si>
+  <si>
+    <t>Vedasandur</t>
+  </si>
+  <si>
+    <t>Irungalur</t>
+  </si>
+  <si>
+    <t>Musiri</t>
+  </si>
+  <si>
+    <t>Thuraiyur</t>
+  </si>
+  <si>
+    <t>Kancheepuram</t>
+  </si>
+  <si>
+    <t>Manapparai</t>
+  </si>
+  <si>
+    <t>Orathanadu</t>
+  </si>
+  <si>
+    <t>Aduthurai</t>
+  </si>
+  <si>
+    <t>Kumbakonam</t>
+  </si>
+  <si>
+    <t>Papanasam</t>
+  </si>
+  <si>
+    <t>Peravurani</t>
+  </si>
+  <si>
+    <t>Ntt  G  Thanjavur</t>
+  </si>
+  <si>
+    <t>Thiruvaiyaru</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pattukottai G </t>
+  </si>
+  <si>
+    <t>Tncsc Pudukkottai</t>
+  </si>
+  <si>
+    <t>Sriperumbudur</t>
+  </si>
+  <si>
+    <t>Aranthanki</t>
+  </si>
+  <si>
+    <t>Alangudi</t>
+  </si>
+  <si>
+    <t>Gandarvakottai</t>
+  </si>
+  <si>
+    <t>Kulathur</t>
+  </si>
+  <si>
+    <t>Ooty</t>
+  </si>
+  <si>
+    <t>Tncsc Godown Kothagiri</t>
+  </si>
+  <si>
+    <t>Coonoor</t>
+  </si>
+  <si>
+    <t>Gudalur</t>
+  </si>
+  <si>
+    <t>Manjoor</t>
+  </si>
+  <si>
+    <t>Wsp Pandalur</t>
+  </si>
+  <si>
+    <t>Thiruvanmiyur</t>
+  </si>
+  <si>
+    <t>Bavani Tak Ii Bhavani</t>
+  </si>
+  <si>
+    <t>Bhavani Tak I Anthiyur</t>
+  </si>
+  <si>
+    <t>Gopi</t>
+  </si>
+  <si>
+    <t>Perundurai</t>
+  </si>
+  <si>
+    <t>Tcms S Gudiyatham</t>
+  </si>
+  <si>
+    <t>Erode Care I</t>
+  </si>
+  <si>
+    <t>Sathy</t>
+  </si>
+  <si>
+    <t>Nandanam</t>
+  </si>
+  <si>
+    <t>Nagapattinam Panangudi</t>
+  </si>
+  <si>
+    <t>Vedaranyam</t>
+  </si>
+  <si>
+    <t>Vellore</t>
+  </si>
+  <si>
+    <t>Keevalur</t>
+  </si>
+  <si>
+    <t>Thirukuvalai</t>
+  </si>
+  <si>
+    <t>Achudamangalam Old</t>
+  </si>
+  <si>
+    <t>Vandavasi</t>
+  </si>
+  <si>
+    <t>Cheyyar</t>
+  </si>
+  <si>
+    <t>O G V Salai</t>
+  </si>
+  <si>
+    <t>Tiruvannamalai</t>
+  </si>
+  <si>
+    <t>Villupuram</t>
+  </si>
+  <si>
+    <t>Tindivanam</t>
+  </si>
+  <si>
+    <t>Vanur</t>
+  </si>
+  <si>
+    <t>Pudupalayam</t>
+  </si>
+  <si>
+    <t>Gingee</t>
+  </si>
+  <si>
+    <t>Perambalur</t>
+  </si>
+  <si>
+    <t>Arni</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pallipet Gdn </t>
+  </si>
+  <si>
+    <t>Mannargudi</t>
+  </si>
+  <si>
+    <t>Moolangudi</t>
+  </si>
+  <si>
+    <t>Keelapandi Old</t>
+  </si>
+  <si>
+    <t>Muthupettai</t>
+  </si>
+  <si>
+    <t>Vedapalayam</t>
+  </si>
+  <si>
+    <t>Tiruvarur</t>
+  </si>
+  <si>
+    <t>Kodavasal</t>
+  </si>
+  <si>
+    <t>Koilvenni</t>
+  </si>
+  <si>
+    <t>Perugauzhnd</t>
+  </si>
+  <si>
+    <t>Valangaiman</t>
+  </si>
+  <si>
+    <t>Kulithalai</t>
+  </si>
+  <si>
+    <t>Polur</t>
+  </si>
+  <si>
+    <t>Karur Tnwc</t>
+  </si>
+  <si>
+    <t>Paramathy</t>
+  </si>
+  <si>
+    <t>Kuppampalayam</t>
+  </si>
+  <si>
+    <t>Rasipuram</t>
+  </si>
+  <si>
+    <t>Tiruchengode</t>
+  </si>
+  <si>
+    <t>Kunnam</t>
+  </si>
+  <si>
+    <t>Panjchetty   Gummidipoondi</t>
+  </si>
+  <si>
+    <t>Thirumazhisai</t>
+  </si>
+  <si>
     <t>Tnwc Thiruvallur</t>
   </si>
   <si>
+    <t>Sembulivaram</t>
+  </si>
+  <si>
+    <t>Uthukottai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thiruthani Gdn </t>
+  </si>
+  <si>
+    <t>Anna Nagar  I</t>
+  </si>
+  <si>
+    <t>Mint</t>
+  </si>
+  <si>
+    <t>Anna Nagar  Ii</t>
+  </si>
+  <si>
+    <t>Thandarampattu</t>
+  </si>
+  <si>
+    <t>Cuddlore Godown</t>
+  </si>
+  <si>
+    <t>Aravakuruchi</t>
+  </si>
+  <si>
+    <t>Thiruvalam</t>
+  </si>
+  <si>
+    <t>Oddanchatram</t>
+  </si>
+  <si>
+    <t>Og Panuruti</t>
+  </si>
+  <si>
+    <t>Og Tittagudi</t>
+  </si>
+  <si>
+    <t>Vepanthattai</t>
+  </si>
+  <si>
+    <t>Og Virudachalam</t>
+  </si>
+  <si>
+    <t>Manaiyeripatti</t>
+  </si>
+  <si>
+    <t>Ariyalur Og</t>
+  </si>
+  <si>
+    <t>Jeyankondam Og</t>
+  </si>
+  <si>
+    <t>Senthurai  Og</t>
+  </si>
+  <si>
+    <t>Kurinjipadi Og</t>
+  </si>
+  <si>
+    <t>Red Hills</t>
+  </si>
+  <si>
+    <t>Tiruchengode Two</t>
+  </si>
+  <si>
+    <t>Gangapuram</t>
+  </si>
+  <si>
+    <t>O G Manalur</t>
+  </si>
+  <si>
+    <t>Tolgate Bg</t>
+  </si>
+  <si>
+    <t>Kadavur Bg</t>
+  </si>
+  <si>
+    <t>Og Kattumannarkoil</t>
+  </si>
+  <si>
+    <t>Meyyanur</t>
+  </si>
+  <si>
+    <t>Tncsc G Edappadi</t>
+  </si>
+  <si>
+    <t>Attur</t>
+  </si>
+  <si>
+    <t>Valapadi</t>
+  </si>
+  <si>
+    <t>Krishnarayapuram Godown</t>
+  </si>
+  <si>
+    <t>Mettur</t>
+  </si>
+  <si>
+    <t>Manmangalam</t>
+  </si>
+  <si>
+    <t>Srirangam Gdn</t>
+  </si>
+  <si>
+    <t>Trichy East Gdn</t>
+  </si>
+  <si>
+    <t>Omalur</t>
+  </si>
+  <si>
+    <t>Trichy West Gdn</t>
+  </si>
+  <si>
+    <t>Gangavalli At Attur</t>
+  </si>
+  <si>
+    <t>Thachampadi</t>
+  </si>
+  <si>
+    <t>Elathur</t>
+  </si>
+  <si>
+    <t>Tncsc G  Sankari</t>
+  </si>
+  <si>
+    <t>Seelanaickanpatti</t>
+  </si>
+  <si>
+    <t>Athoor</t>
+  </si>
+  <si>
+    <t>Alathur</t>
+  </si>
+  <si>
+    <t>Palani</t>
+  </si>
+  <si>
+    <t>Dindigul</t>
+  </si>
+  <si>
+    <t>Natham</t>
+  </si>
+  <si>
+    <t>Kodaikanal</t>
+  </si>
+  <si>
+    <t>Tirukoilur   RThreeFour</t>
+  </si>
+  <si>
+    <t>Uludurpet   RThreeFour</t>
+  </si>
+  <si>
+    <t>Kallakuruchi   RThreeFour</t>
+  </si>
+  <si>
+    <t>Sankarapuram   RThreeFour</t>
+  </si>
+  <si>
+    <t>Og Chinnasalem   RThreeFour</t>
+  </si>
+  <si>
+    <t>Chengallpatu   RFiveEight</t>
+  </si>
+  <si>
+    <t>Vallam Godown   RFiveEight</t>
+  </si>
+  <si>
+    <t>Vilvarayanallur   RFiveEight</t>
+  </si>
+  <si>
+    <t>Thirukalukundarm   RFiveEight</t>
+  </si>
+  <si>
+    <t>Madurantakam   RFiveEight</t>
+  </si>
+  <si>
+    <t>Ambur   RSixZero</t>
+  </si>
+  <si>
+    <t>Tirupathur Kunichi   RSixZero</t>
+  </si>
+  <si>
+    <t>Vaniyambadi   RSixZero</t>
+  </si>
+  <si>
+    <t>Wallaja   RFiveNine</t>
+  </si>
+  <si>
+    <t>Arcot Melnathampakkam   RFiveNine</t>
+  </si>
+  <si>
+    <t>Arakonam   RFiveNine</t>
+  </si>
+  <si>
+    <t>Tharangambadi Tk Godown   RThreeOne</t>
+  </si>
+  <si>
+    <t>Sirkali Tk Godown   RThreeOne</t>
+  </si>
+  <si>
+    <t>Mayiladuthurai Tk Godown   RThreeOne</t>
+  </si>
+  <si>
+    <t>Kandachipuram</t>
+  </si>
+  <si>
+    <t>Madhavaram Two</t>
+  </si>
+  <si>
+    <t>Natrampalli</t>
+  </si>
+  <si>
+    <t>Sethirabalapuram</t>
+  </si>
+  <si>
+    <t>Kattupakkam</t>
+  </si>
+  <si>
+    <t>Vempakkam</t>
+  </si>
+  <si>
+    <t>Cwc Chromepet</t>
+  </si>
+  <si>
+    <t>Sullerumbu</t>
+  </si>
+  <si>
+    <t>Guziliyamparai</t>
+  </si>
+  <si>
+    <t>Anaicut Godown</t>
+  </si>
+  <si>
+    <t>Marungapuri</t>
+  </si>
+  <si>
+    <t>Pernampet</t>
+  </si>
+  <si>
+    <t>R K Pettai</t>
+  </si>
+  <si>
+    <t>Walajabad</t>
+  </si>
+  <si>
+    <t>South Chennai</t>
+  </si>
+  <si>
+    <t>Thiruchirapalli</t>
+  </si>
+  <si>
+    <t>Kanchipuram</t>
+  </si>
+  <si>
+    <t>Thanjavur</t>
+  </si>
+  <si>
+    <t>Pudukkottai</t>
+  </si>
+  <si>
+    <t>Nilgiris</t>
+  </si>
+  <si>
+    <t>Erode</t>
+  </si>
+  <si>
+    <t>Nagapattinam</t>
+  </si>
+  <si>
+    <t>Thiruvarur</t>
+  </si>
+  <si>
+    <t>Thiruvannamalai</t>
+  </si>
+  <si>
+    <t>Viluppuram</t>
+  </si>
+  <si>
     <t>Thiruvallur</t>
   </si>
   <si>
+    <t>Karur</t>
+  </si>
+  <si>
+    <t>Namakkal</t>
+  </si>
+  <si>
+    <t>North Chennai</t>
+  </si>
+  <si>
+    <t>Cuddalore</t>
+  </si>
+  <si>
+    <t>Ariyalur</t>
+  </si>
+  <si>
+    <t>Salem</t>
+  </si>
+  <si>
+    <t>Kallakurichi</t>
+  </si>
+  <si>
+    <t>Chengalpet</t>
+  </si>
+  <si>
+    <t>Tirupathur</t>
+  </si>
+  <si>
+    <t>Ranipet</t>
+  </si>
+  <si>
+    <t>Mayiladuthurai</t>
+  </si>
+  <si>
+    <t>13.05174</t>
+  </si>
+  <si>
+    <t>10.16155</t>
+  </si>
+  <si>
+    <t>10.52538</t>
+  </si>
+  <si>
+    <t>10.96435</t>
+  </si>
+  <si>
+    <t>10.96156</t>
+  </si>
+  <si>
+    <t>11.13023</t>
+  </si>
+  <si>
+    <t>12.86381</t>
+  </si>
+  <si>
+    <t>10.64501</t>
+  </si>
+  <si>
+    <t>10.63221</t>
+  </si>
+  <si>
+    <t>11.02379</t>
+  </si>
+  <si>
+    <t>10.95419</t>
+  </si>
+  <si>
+    <t>10.92245</t>
+  </si>
+  <si>
+    <t>10.30179</t>
+  </si>
+  <si>
+    <t>10.76955</t>
+  </si>
+  <si>
+    <t>10.88186</t>
+  </si>
+  <si>
+    <t>10.47255</t>
+  </si>
+  <si>
+    <t>10.39185</t>
+  </si>
+  <si>
+    <t>12.97438</t>
+  </si>
+  <si>
+    <t>10.2002</t>
+  </si>
+  <si>
+    <t>10.37979</t>
+  </si>
+  <si>
+    <t>10.56192</t>
+  </si>
+  <si>
+    <t>10.55767</t>
+  </si>
+  <si>
+    <t>11.41109</t>
+  </si>
+  <si>
+    <t>11.42447</t>
+  </si>
+  <si>
+    <t>11.34996</t>
+  </si>
+  <si>
+    <t>11.49867</t>
+  </si>
+  <si>
+    <t>11.48798</t>
+  </si>
+  <si>
+    <t>12.98297</t>
+  </si>
+  <si>
+    <t>11.46197</t>
+  </si>
+  <si>
+    <t>11.56029</t>
+  </si>
+  <si>
+    <t>11.45776</t>
+  </si>
+  <si>
+    <t>11.24831</t>
+  </si>
+  <si>
+    <t>12.97697</t>
+  </si>
+  <si>
+    <t>11.29475</t>
+  </si>
+  <si>
+    <t>11.48433</t>
+  </si>
+  <si>
+    <t>13.03011</t>
+  </si>
+  <si>
+    <t>10.83013</t>
+  </si>
+  <si>
+    <t>10.41191</t>
+  </si>
+  <si>
+    <t>12.88384</t>
+  </si>
+  <si>
+    <t>10.75578</t>
+  </si>
+  <si>
+    <t>10.62287</t>
+  </si>
+  <si>
+    <t>10.88308</t>
+  </si>
+  <si>
+    <t>12.48707</t>
+  </si>
+  <si>
+    <t>12.71323</t>
+  </si>
+  <si>
+    <t>12.06494</t>
+  </si>
+  <si>
+    <t>12.22985</t>
+  </si>
+  <si>
+    <t>11.9422</t>
+  </si>
+  <si>
+    <t>12.25404</t>
+  </si>
+  <si>
+    <t>12.02794</t>
+  </si>
+  <si>
+    <t>12.35256</t>
+  </si>
+  <si>
+    <t>12.25059</t>
+  </si>
+  <si>
+    <t>11.23467</t>
+  </si>
+  <si>
+    <t>12.66498</t>
+  </si>
+  <si>
+    <t>13.30374</t>
+  </si>
+  <si>
+    <t>10.63178</t>
+  </si>
+  <si>
+    <t>10.82939</t>
+  </si>
+  <si>
+    <t>10.41495</t>
+  </si>
+  <si>
+    <t>12.61204</t>
+  </si>
+  <si>
+    <t>10.76805</t>
+  </si>
+  <si>
+    <t>10.84844</t>
+  </si>
+  <si>
+    <t>10.77718</t>
+  </si>
+  <si>
+    <t>10.47995</t>
+  </si>
+  <si>
+    <t>10.87001</t>
+  </si>
+  <si>
+    <t>12.51484</t>
+  </si>
+  <si>
+    <t>10.95922</t>
+  </si>
+  <si>
+    <t>11.15758</t>
+  </si>
+  <si>
+    <t>11.17515</t>
+  </si>
+  <si>
+    <t>11.44165</t>
+  </si>
+  <si>
+    <t>11.40676</t>
+  </si>
+  <si>
+    <t>11.15279</t>
+  </si>
+  <si>
+    <t>13.29966</t>
+  </si>
+  <si>
+    <t>13.06124</t>
+  </si>
+  <si>
     <t>13.13195</t>
   </si>
   <si>
+    <t>13.1991</t>
+  </si>
+  <si>
+    <t>13.28475</t>
+  </si>
+  <si>
+    <t>13.17392</t>
+  </si>
+  <si>
+    <t>13.08651</t>
+  </si>
+  <si>
+    <t>13.10566</t>
+  </si>
+  <si>
+    <t>13.08652</t>
+  </si>
+  <si>
+    <t>12.14644</t>
+  </si>
+  <si>
+    <t>11.76142</t>
+  </si>
+  <si>
+    <t>10.94658</t>
+  </si>
+  <si>
+    <t>12.97515</t>
+  </si>
+  <si>
+    <t>10.4726</t>
+  </si>
+  <si>
+    <t>11.76408</t>
+  </si>
+  <si>
+    <t>11.39956</t>
+  </si>
+  <si>
+    <t>11.36959</t>
+  </si>
+  <si>
+    <t>11.52126</t>
+  </si>
+  <si>
+    <t>10.73726</t>
+  </si>
+  <si>
+    <t>11.14938</t>
+  </si>
+  <si>
+    <t>11.20857</t>
+  </si>
+  <si>
+    <t>11.25424</t>
+  </si>
+  <si>
+    <t>11.63566</t>
+  </si>
+  <si>
+    <t>13.19934</t>
+  </si>
+  <si>
+    <t>11.41985</t>
+  </si>
+  <si>
+    <t>11.36601</t>
+  </si>
+  <si>
+    <t>11.41618</t>
+  </si>
+  <si>
+    <t>13.14409</t>
+  </si>
+  <si>
+    <t>10.75937</t>
+  </si>
+  <si>
+    <t>11.26682</t>
+  </si>
+  <si>
+    <t>11.65691</t>
+  </si>
+  <si>
+    <t>11.55137</t>
+  </si>
+  <si>
+    <t>11.58601</t>
+  </si>
+  <si>
+    <t>11.65706</t>
+  </si>
+  <si>
+    <t>11.81885</t>
+  </si>
+  <si>
+    <t>10.95929</t>
+  </si>
+  <si>
+    <t>10.80826</t>
+  </si>
+  <si>
+    <t>10.78775</t>
+  </si>
+  <si>
+    <t>11.73075</t>
+  </si>
+  <si>
+    <t>10.8065</t>
+  </si>
+  <si>
+    <t>11.49347</t>
+  </si>
+  <si>
+    <t>12.48271</t>
+  </si>
+  <si>
+    <t>12.44474</t>
+  </si>
+  <si>
+    <t>11.4377</t>
+  </si>
+  <si>
+    <t>11.62124</t>
+  </si>
+  <si>
+    <t>10.25588</t>
+  </si>
+  <si>
+    <t>11.0873</t>
+  </si>
+  <si>
+    <t>10.4486</t>
+  </si>
+  <si>
+    <t>10.3471</t>
+  </si>
+  <si>
+    <t>10.23208</t>
+  </si>
+  <si>
+    <t>10.23253</t>
+  </si>
+  <si>
+    <t>11.9831</t>
+  </si>
+  <si>
+    <t>11.69058</t>
+  </si>
+  <si>
+    <t>11.72876</t>
+  </si>
+  <si>
+    <t>11.873</t>
+  </si>
+  <si>
+    <t>11.62955</t>
+  </si>
+  <si>
+    <t>12.71699</t>
+  </si>
+  <si>
+    <t>12.71695</t>
+  </si>
+  <si>
+    <t>12.47755</t>
+  </si>
+  <si>
+    <t>12.59518</t>
+  </si>
+  <si>
+    <t>12.49033</t>
+  </si>
+  <si>
+    <t>12.84124</t>
+  </si>
+  <si>
+    <t>12.4439</t>
+  </si>
+  <si>
+    <t>12.66906</t>
+  </si>
+  <si>
+    <t>12.9137</t>
+  </si>
+  <si>
+    <t>12.78594</t>
+  </si>
+  <si>
+    <t>13.07205</t>
+  </si>
+  <si>
+    <t>11.12656</t>
+  </si>
+  <si>
+    <t>11.27321</t>
+  </si>
+  <si>
+    <t>11.09028</t>
+  </si>
+  <si>
+    <t>11.98341</t>
+  </si>
+  <si>
+    <t>13.15217</t>
+  </si>
+  <si>
+    <t>12.57908</t>
+  </si>
+  <si>
+    <t>11.07607</t>
+  </si>
+  <si>
+    <t>13.04216</t>
+  </si>
+  <si>
+    <t>12.76163</t>
+  </si>
+  <si>
+    <t>12.93802</t>
+  </si>
+  <si>
+    <t>10.50723</t>
+  </si>
+  <si>
+    <t>10.73867</t>
+  </si>
+  <si>
+    <t>12.85391</t>
+  </si>
+  <si>
+    <t>10.43484518</t>
+  </si>
+  <si>
+    <t>12.92446</t>
+  </si>
+  <si>
+    <t>13.17482</t>
+  </si>
+  <si>
+    <t>12.79834587</t>
+  </si>
+  <si>
+    <t>80.25829</t>
+  </si>
+  <si>
+    <t>77.74247</t>
+  </si>
+  <si>
+    <t>77.92971</t>
+  </si>
+  <si>
+    <t>78.76272</t>
+  </si>
+  <si>
+    <t>78.44363</t>
+  </si>
+  <si>
+    <t>78.58531</t>
+  </si>
+  <si>
+    <t>79.67131</t>
+  </si>
+  <si>
+    <t>78.45789</t>
+  </si>
+  <si>
+    <t>79.24759</t>
+  </si>
+  <si>
+    <t>79.48877</t>
+  </si>
+  <si>
+    <t>79.39575</t>
+  </si>
+  <si>
+    <t>79.2752</t>
+  </si>
+  <si>
+    <t>79.21391</t>
+  </si>
+  <si>
+    <t>79.11893</t>
+  </si>
+  <si>
+    <t>79.10889</t>
+  </si>
+  <si>
+    <t>79.29994</t>
+  </si>
+  <si>
+    <t>78.78945</t>
+  </si>
+  <si>
+    <t>79.9609</t>
+  </si>
+  <si>
+    <t>78.96895</t>
+  </si>
+  <si>
+    <t>78.99511</t>
+  </si>
+  <si>
+    <t>79.05688</t>
+  </si>
+  <si>
+    <t>78.7782</t>
+  </si>
+  <si>
+    <t>76.70064</t>
+  </si>
+  <si>
+    <t>76.86421</t>
+  </si>
+  <si>
+    <t>76.79655</t>
+  </si>
+  <si>
+    <t>76.48224</t>
+  </si>
+  <si>
+    <t>76.34422</t>
+  </si>
+  <si>
+    <t>80.25099</t>
+  </si>
+  <si>
+    <t>77.66334</t>
+  </si>
+  <si>
+    <t>77.50863</t>
+  </si>
+  <si>
+    <t>77.40008</t>
+  </si>
+  <si>
+    <t>77.62526</t>
+  </si>
+  <si>
+    <t>78.87463</t>
+  </si>
+  <si>
+    <t>77.69371</t>
+  </si>
+  <si>
+    <t>77.22996</t>
+  </si>
+  <si>
+    <t>80.24278</t>
+  </si>
+  <si>
+    <t>79.82775</t>
+  </si>
+  <si>
+    <t>79.84799</t>
+  </si>
+  <si>
+    <t>79.12984</t>
+  </si>
+  <si>
+    <t>79.7426</t>
+  </si>
+  <si>
+    <t>79.73224</t>
+  </si>
+  <si>
+    <t>79.58019</t>
+  </si>
+  <si>
+    <t>79.60055</t>
+  </si>
+  <si>
+    <t>79.52592</t>
+  </si>
+  <si>
+    <t>79.55032</t>
+  </si>
+  <si>
+    <t>79.03961</t>
+  </si>
+  <si>
+    <t>79.48792</t>
+  </si>
+  <si>
+    <t>79.63874</t>
+  </si>
+  <si>
+    <t>79.76638</t>
+  </si>
+  <si>
+    <t>78.87075</t>
+  </si>
+  <si>
+    <t>79.43034</t>
+  </si>
+  <si>
+    <t>78.88156</t>
+  </si>
+  <si>
+    <t>79.2968</t>
+  </si>
+  <si>
+    <t>79.44649</t>
+  </si>
+  <si>
+    <t>79.442</t>
+  </si>
+  <si>
+    <t>79.4048</t>
+  </si>
+  <si>
+    <t>79.49482</t>
+  </si>
+  <si>
+    <t>79.73038</t>
+  </si>
+  <si>
+    <t>79.6269</t>
+  </si>
+  <si>
+    <t>79.48345</t>
+  </si>
+  <si>
+    <t>79.37489</t>
+  </si>
+  <si>
+    <t>79.49532</t>
+  </si>
+  <si>
+    <t>78.38732</t>
+  </si>
+  <si>
+    <t>79.1294</t>
+  </si>
+  <si>
+    <t>78.1088</t>
+  </si>
+  <si>
+    <t>78.02253</t>
+  </si>
+  <si>
+    <t>78.19898</t>
+  </si>
+  <si>
+    <t>78.20692</t>
+  </si>
+  <si>
+    <t>77.92444</t>
+  </si>
+  <si>
+    <t>79.06359</t>
+  </si>
+  <si>
+    <t>80.14788</t>
+  </si>
+  <si>
+    <t>80.0484</t>
+  </si>
+  <si>
     <t>79.90671</t>
   </si>
   <si>
+    <t>80.15104</t>
+  </si>
+  <si>
+    <t>79.88796</t>
+  </si>
+  <si>
+    <t>79.59486</t>
+  </si>
+  <si>
+    <t>80.21687</t>
+  </si>
+  <si>
+    <t>80.27905</t>
+  </si>
+  <si>
+    <t>80.21679</t>
+  </si>
+  <si>
+    <t>78.98364</t>
+  </si>
+  <si>
+    <t>79.75304</t>
+  </si>
+  <si>
+    <t>77.83781</t>
+  </si>
+  <si>
+    <t>79.24167</t>
+  </si>
+  <si>
+    <t>77.78538</t>
+  </si>
+  <si>
+    <t>79.54914</t>
+  </si>
+  <si>
+    <t>79.17294</t>
+  </si>
+  <si>
+    <t>78.79501</t>
+  </si>
+  <si>
+    <t>79.33991</t>
+  </si>
+  <si>
+    <t>78.92043</t>
+  </si>
+  <si>
+    <t>79.06606</t>
+  </si>
+  <si>
+    <t>79.38768</t>
+  </si>
+  <si>
+    <t>79.17812</t>
+  </si>
+  <si>
+    <t>79.54699</t>
+  </si>
+  <si>
+    <t>80.1517</t>
+  </si>
+  <si>
+    <t>77.92618</t>
+  </si>
+  <si>
+    <t>77.65787</t>
+  </si>
+  <si>
+    <t>79.68593</t>
+  </si>
+  <si>
+    <t>80.29672</t>
+  </si>
+  <si>
+    <t>78.19688</t>
+  </si>
+  <si>
+    <t>79.55477</t>
+  </si>
+  <si>
+    <t>78.14767</t>
+  </si>
+  <si>
+    <t>77.85528</t>
+  </si>
+  <si>
+    <t>78.59908</t>
+  </si>
+  <si>
+    <t>78.33625</t>
+  </si>
+  <si>
+    <t>77.85816</t>
+  </si>
+  <si>
+    <t>78.10887</t>
+  </si>
+  <si>
+    <t>78.61972</t>
+  </si>
+  <si>
+    <t>78.69468</t>
+  </si>
+  <si>
+    <t>78.0392</t>
+  </si>
+  <si>
+    <t>78.62039</t>
+  </si>
+  <si>
+    <t>78.63906</t>
+  </si>
+  <si>
+    <t>79.28352</t>
+  </si>
+  <si>
+    <t>79.05933</t>
+  </si>
+  <si>
+    <t>77.87623</t>
+  </si>
+  <si>
+    <t>78.14655</t>
+  </si>
+  <si>
+    <t>77.86348</t>
+  </si>
+  <si>
+    <t>78.84349</t>
+  </si>
+  <si>
+    <t>77.52501</t>
+  </si>
+  <si>
+    <t>77.98808</t>
+  </si>
+  <si>
+    <t>78.22209</t>
+  </si>
+  <si>
+    <t>77.46852</t>
+  </si>
+  <si>
+    <t>79.22732</t>
+  </si>
+  <si>
+    <t>79.29882</t>
+  </si>
+  <si>
+    <t>78.95962</t>
+  </si>
+  <si>
+    <t>78.91318</t>
+  </si>
+  <si>
+    <t>78.86658</t>
+  </si>
+  <si>
+    <t>79.95632</t>
+  </si>
+  <si>
+    <t>80.13757</t>
+  </si>
+  <si>
+    <t>79.88866</t>
+  </si>
+  <si>
+    <t>80.06973</t>
+  </si>
+  <si>
+    <t>79.8676</t>
+  </si>
+  <si>
+    <t>78.79122</t>
+  </si>
+  <si>
+    <t>78.5127</t>
+  </si>
+  <si>
+    <t>78.64486</t>
+  </si>
+  <si>
+    <t>79.36932</t>
+  </si>
+  <si>
+    <t>79.38255</t>
+  </si>
+  <si>
+    <t>79.66579</t>
+  </si>
+  <si>
+    <t>79.7551</t>
+  </si>
+  <si>
+    <t>79.7234</t>
+  </si>
+  <si>
+    <t>79.61826</t>
+  </si>
+  <si>
+    <t>79.2279</t>
+  </si>
+  <si>
+    <t>80.24039</t>
+  </si>
+  <si>
+    <t>78.46369</t>
+  </si>
+  <si>
+    <t>79.58224</t>
+  </si>
+  <si>
+    <t>80.12019</t>
+  </si>
+  <si>
+    <t>79.51445</t>
+  </si>
+  <si>
+    <t>80.1381</t>
+  </si>
+  <si>
+    <t>77.8562</t>
+  </si>
+  <si>
+    <t>78.0694</t>
+  </si>
+  <si>
+    <t>78.88894</t>
+  </si>
+  <si>
+    <t>78.43713064</t>
+  </si>
+  <si>
+    <t>78.70454</t>
+  </si>
+  <si>
+    <t>79.45377</t>
+  </si>
+  <si>
+    <t>79.81905544</t>
+  </si>
+  <si>
     <t>State Name</t>
   </si>
   <si>
@@ -83,21 +1637,6 @@
     <t>Allotment_FRice</t>
   </si>
   <si>
-    <t>Southchennai</t>
-  </si>
-  <si>
-    <t>Vellore</t>
-  </si>
-  <si>
-    <t>Ranipet</t>
-  </si>
-  <si>
-    <t>Chengalpet</t>
-  </si>
-  <si>
-    <t>Thiruvannamalai</t>
-  </si>
-  <si>
     <t>Madurai</t>
   </si>
   <si>
@@ -119,51 +1658,18 @@
     <t>Kanyakumari</t>
   </si>
   <si>
-    <t>Dindigul</t>
-  </si>
-  <si>
-    <t>Erode</t>
-  </si>
-  <si>
     <t>Krishnagiri</t>
   </si>
   <si>
     <t>Tiruppur</t>
   </si>
   <si>
-    <t>Namakkal</t>
-  </si>
-  <si>
     <t>Dharmapuri</t>
   </si>
   <si>
     <t>Coimbatore</t>
   </si>
   <si>
-    <t>Salem</t>
-  </si>
-  <si>
-    <t>Thanjavur</t>
-  </si>
-  <si>
-    <t>Mayiladuthurai</t>
-  </si>
-  <si>
-    <t>Pudukkottai</t>
-  </si>
-  <si>
-    <t>Thiruchirapalli</t>
-  </si>
-  <si>
-    <t>Kallakurichi</t>
-  </si>
-  <si>
-    <t>Viluppuram</t>
-  </si>
-  <si>
-    <t>Cuddalore</t>
-  </si>
-  <si>
     <t>FSD Egmore</t>
   </si>
   <si>
@@ -705,21 +2211,6 @@
   </si>
   <si>
     <t>351700</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>1000</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>5</t>
   </si>
 </sst>
 </file>
@@ -1077,7 +2568,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H159"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1108,28 +2599,4110 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2" t="s">
+        <v>199</v>
+      </c>
+      <c r="D2" t="s">
+        <v>222</v>
+      </c>
+      <c r="E2" t="s">
+        <v>376</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>9312.4</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3">
+        <v>100</v>
+      </c>
+      <c r="B3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3" t="s">
+        <v>163</v>
+      </c>
+      <c r="D3" t="s">
+        <v>223</v>
+      </c>
+      <c r="E3" t="s">
+        <v>377</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>6637.35</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4">
+        <v>110</v>
+      </c>
+      <c r="B4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4" t="s">
+        <v>163</v>
+      </c>
+      <c r="D4" t="s">
+        <v>224</v>
+      </c>
+      <c r="E4" t="s">
+        <v>378</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>5817.25</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5">
+        <v>111</v>
+      </c>
+      <c r="B5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5" t="s">
+        <v>200</v>
+      </c>
+      <c r="D5" t="s">
+        <v>225</v>
+      </c>
+      <c r="E5" t="s">
+        <v>379</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>13225.95</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6">
+        <v>113</v>
+      </c>
+      <c r="B6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" t="s">
+        <v>200</v>
+      </c>
+      <c r="D6" t="s">
+        <v>226</v>
+      </c>
+      <c r="E6" t="s">
+        <v>380</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>9144.450000000001</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7">
+        <v>114</v>
+      </c>
+      <c r="B7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7" t="s">
+        <v>200</v>
+      </c>
+      <c r="D7" t="s">
+        <v>227</v>
+      </c>
+      <c r="E7" t="s">
+        <v>381</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>11498.5</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" t="s">
+        <v>201</v>
+      </c>
+      <c r="D8" t="s">
+        <v>228</v>
+      </c>
+      <c r="E8" t="s">
+        <v>382</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>11893.35</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9">
+        <v>120</v>
+      </c>
+      <c r="B9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C9" t="s">
+        <v>200</v>
+      </c>
+      <c r="D9" t="s">
+        <v>229</v>
+      </c>
+      <c r="E9" t="s">
+        <v>383</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>12688.7</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10">
+        <v>137</v>
+      </c>
+      <c r="B10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C10" t="s">
+        <v>202</v>
+      </c>
+      <c r="D10" t="s">
+        <v>230</v>
+      </c>
+      <c r="E10" t="s">
+        <v>384</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>7573.3</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11">
+        <v>147</v>
+      </c>
+      <c r="B11" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" t="s">
+        <v>202</v>
+      </c>
+      <c r="D11" t="s">
+        <v>231</v>
+      </c>
+      <c r="E11" t="s">
+        <v>385</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>8346.1</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12">
+        <v>149</v>
+      </c>
+      <c r="B12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C12" t="s">
+        <v>202</v>
+      </c>
+      <c r="D12" t="s">
+        <v>232</v>
+      </c>
+      <c r="E12" t="s">
+        <v>386</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>11815.4</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13">
+        <v>153</v>
+      </c>
+      <c r="B13" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13" t="s">
+        <v>202</v>
+      </c>
+      <c r="D13" t="s">
+        <v>233</v>
+      </c>
+      <c r="E13" t="s">
+        <v>387</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>7347.6</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14">
+        <v>158</v>
+      </c>
+      <c r="B14" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" t="s">
+        <v>202</v>
+      </c>
+      <c r="D14" t="s">
+        <v>234</v>
+      </c>
+      <c r="E14" t="s">
+        <v>388</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>9620.65</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15">
+        <v>161</v>
+      </c>
+      <c r="B15" t="s">
+        <v>54</v>
+      </c>
+      <c r="C15" t="s">
+        <v>202</v>
+      </c>
+      <c r="D15" t="s">
+        <v>235</v>
+      </c>
+      <c r="E15" t="s">
+        <v>389</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>11592.1</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16">
+        <v>162</v>
+      </c>
+      <c r="B16" t="s">
+        <v>55</v>
+      </c>
+      <c r="C16" t="s">
+        <v>202</v>
+      </c>
+      <c r="D16" t="s">
+        <v>236</v>
+      </c>
+      <c r="E16" t="s">
+        <v>390</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>6696.65</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17">
+        <v>163</v>
+      </c>
+      <c r="B17" t="s">
+        <v>56</v>
+      </c>
+      <c r="C17" t="s">
+        <v>202</v>
+      </c>
+      <c r="D17" t="s">
+        <v>237</v>
+      </c>
+      <c r="E17" t="s">
+        <v>391</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>14443.5</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18">
+        <v>168</v>
+      </c>
+      <c r="B18" t="s">
+        <v>57</v>
+      </c>
+      <c r="C18" t="s">
+        <v>203</v>
+      </c>
+      <c r="D18" t="s">
+        <v>238</v>
+      </c>
+      <c r="E18" t="s">
+        <v>392</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>6051.5</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19">
+        <v>17</v>
+      </c>
+      <c r="B19" t="s">
+        <v>58</v>
+      </c>
+      <c r="C19" t="s">
+        <v>201</v>
+      </c>
+      <c r="D19" t="s">
+        <v>239</v>
+      </c>
+      <c r="E19" t="s">
+        <v>393</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>13415</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20">
+        <v>171</v>
+      </c>
+      <c r="B20" t="s">
+        <v>59</v>
+      </c>
+      <c r="C20" t="s">
+        <v>203</v>
+      </c>
+      <c r="D20" t="s">
+        <v>240</v>
+      </c>
+      <c r="E20" t="s">
+        <v>394</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>388.6</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21">
+        <v>175</v>
+      </c>
+      <c r="B21" t="s">
+        <v>60</v>
+      </c>
+      <c r="C21" t="s">
+        <v>203</v>
+      </c>
+      <c r="D21" t="s">
+        <v>241</v>
+      </c>
+      <c r="E21" t="s">
+        <v>395</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>6799.5</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22">
+        <v>176</v>
+      </c>
+      <c r="B22" t="s">
+        <v>61</v>
+      </c>
+      <c r="C22" t="s">
+        <v>203</v>
+      </c>
+      <c r="D22" t="s">
+        <v>242</v>
+      </c>
+      <c r="E22" t="s">
+        <v>396</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>595.65</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23">
+        <v>177</v>
+      </c>
+      <c r="B23" t="s">
+        <v>62</v>
+      </c>
+      <c r="C23" t="s">
+        <v>203</v>
+      </c>
+      <c r="D23" t="s">
+        <v>243</v>
+      </c>
+      <c r="E23" t="s">
+        <v>397</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>436.6</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24">
+        <v>191</v>
+      </c>
+      <c r="B24" t="s">
+        <v>63</v>
+      </c>
+      <c r="C24" t="s">
+        <v>204</v>
+      </c>
+      <c r="D24" t="s">
+        <v>244</v>
+      </c>
+      <c r="E24" t="s">
+        <v>398</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>7405.2</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25">
+        <v>192</v>
+      </c>
+      <c r="B25" t="s">
+        <v>64</v>
+      </c>
+      <c r="C25" t="s">
+        <v>204</v>
+      </c>
+      <c r="D25" t="s">
+        <v>245</v>
+      </c>
+      <c r="E25" t="s">
+        <v>399</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>4066</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26">
+        <v>195</v>
+      </c>
+      <c r="B26" t="s">
+        <v>65</v>
+      </c>
+      <c r="C26" t="s">
+        <v>204</v>
+      </c>
+      <c r="D26" t="s">
+        <v>246</v>
+      </c>
+      <c r="E26" t="s">
+        <v>400</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>3728.15</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27">
+        <v>196</v>
+      </c>
+      <c r="B27" t="s">
+        <v>66</v>
+      </c>
+      <c r="C27" t="s">
+        <v>204</v>
+      </c>
+      <c r="D27" t="s">
+        <v>247</v>
+      </c>
+      <c r="E27" t="s">
+        <v>401</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>4616.7</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28">
+        <v>197</v>
+      </c>
+      <c r="B28" t="s">
+        <v>67</v>
+      </c>
+      <c r="C28" t="s">
+        <v>204</v>
+      </c>
+      <c r="D28" t="s">
+        <v>248</v>
+      </c>
+      <c r="E28" t="s">
+        <v>402</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <v>3374.75</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29">
+        <v>198</v>
+      </c>
+      <c r="B29" t="s">
+        <v>68</v>
+      </c>
+      <c r="C29" t="s">
+        <v>204</v>
+      </c>
+      <c r="D29" t="s">
+        <v>248</v>
+      </c>
+      <c r="E29" t="s">
+        <v>402</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29">
+        <v>1686.45</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30">
+        <v>2</v>
+      </c>
+      <c r="B30" t="s">
+        <v>69</v>
+      </c>
+      <c r="C30" t="s">
+        <v>199</v>
+      </c>
+      <c r="D30" t="s">
+        <v>249</v>
+      </c>
+      <c r="E30" t="s">
+        <v>403</v>
+      </c>
+      <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="G30">
+        <v>13393.4</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31">
+        <v>252</v>
+      </c>
+      <c r="B31" t="s">
+        <v>70</v>
+      </c>
+      <c r="C31" t="s">
+        <v>205</v>
+      </c>
+      <c r="D31" t="s">
+        <v>250</v>
+      </c>
+      <c r="E31" t="s">
+        <v>404</v>
+      </c>
+      <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31">
+        <v>8064.05</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32">
+        <v>253</v>
+      </c>
+      <c r="B32" t="s">
+        <v>71</v>
+      </c>
+      <c r="C32" t="s">
+        <v>205</v>
+      </c>
+      <c r="D32" t="s">
+        <v>251</v>
+      </c>
+      <c r="E32" t="s">
+        <v>405</v>
+      </c>
+      <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="G32">
+        <v>8098.9</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33">
+        <v>257</v>
+      </c>
+      <c r="B33" t="s">
+        <v>72</v>
+      </c>
+      <c r="C33" t="s">
+        <v>205</v>
+      </c>
+      <c r="D33" t="s">
+        <v>252</v>
+      </c>
+      <c r="E33" t="s">
+        <v>406</v>
+      </c>
+      <c r="F33">
+        <v>0</v>
+      </c>
+      <c r="G33">
+        <v>8619.1</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34">
+        <v>261</v>
+      </c>
+      <c r="B34" t="s">
+        <v>73</v>
+      </c>
+      <c r="C34" t="s">
+        <v>205</v>
+      </c>
+      <c r="D34" t="s">
+        <v>253</v>
+      </c>
+      <c r="E34" t="s">
+        <v>407</v>
+      </c>
+      <c r="F34">
+        <v>0</v>
+      </c>
+      <c r="G34">
+        <v>6772.55</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35">
+        <v>27</v>
+      </c>
+      <c r="B35" t="s">
+        <v>74</v>
+      </c>
+      <c r="C35" t="s">
+        <v>80</v>
+      </c>
+      <c r="D35" t="s">
+        <v>254</v>
+      </c>
+      <c r="E35" t="s">
+        <v>408</v>
+      </c>
+      <c r="F35">
+        <v>0</v>
+      </c>
+      <c r="G35">
+        <v>8824.4</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36">
+        <v>281</v>
+      </c>
+      <c r="B36" t="s">
+        <v>75</v>
+      </c>
+      <c r="C36" t="s">
+        <v>205</v>
+      </c>
+      <c r="D36" t="s">
+        <v>255</v>
+      </c>
+      <c r="E36" t="s">
+        <v>409</v>
+      </c>
+      <c r="F36">
+        <v>0</v>
+      </c>
+      <c r="G36">
+        <v>10756.1</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37">
+        <v>288</v>
+      </c>
+      <c r="B37" t="s">
+        <v>76</v>
+      </c>
+      <c r="C37" t="s">
+        <v>205</v>
+      </c>
+      <c r="D37" t="s">
+        <v>256</v>
+      </c>
+      <c r="E37" t="s">
+        <v>410</v>
+      </c>
+      <c r="F37">
+        <v>0</v>
+      </c>
+      <c r="G37">
+        <v>12585</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38">
+        <v>3</v>
+      </c>
+      <c r="B38" t="s">
+        <v>77</v>
+      </c>
+      <c r="C38" t="s">
+        <v>199</v>
+      </c>
+      <c r="D38" t="s">
+        <v>257</v>
+      </c>
+      <c r="E38" t="s">
+        <v>411</v>
+      </c>
+      <c r="F38">
+        <v>0</v>
+      </c>
+      <c r="G38">
+        <v>13109.3</v>
+      </c>
+      <c r="H38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39">
+        <v>317</v>
+      </c>
+      <c r="B39" t="s">
+        <v>78</v>
+      </c>
+      <c r="C39" t="s">
+        <v>206</v>
+      </c>
+      <c r="D39" t="s">
+        <v>258</v>
+      </c>
+      <c r="E39" t="s">
+        <v>412</v>
+      </c>
+      <c r="F39">
+        <v>0</v>
+      </c>
+      <c r="G39">
+        <v>6742.3</v>
+      </c>
+      <c r="H39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40">
+        <v>320</v>
+      </c>
+      <c r="B40" t="s">
+        <v>79</v>
+      </c>
+      <c r="C40" t="s">
+        <v>206</v>
+      </c>
+      <c r="D40" t="s">
+        <v>259</v>
+      </c>
+      <c r="E40" t="s">
+        <v>413</v>
+      </c>
+      <c r="F40">
+        <v>0</v>
+      </c>
+      <c r="G40">
+        <v>8553.35</v>
+      </c>
+      <c r="H40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41">
+        <v>34</v>
+      </c>
+      <c r="B41" t="s">
+        <v>80</v>
+      </c>
+      <c r="C41" t="s">
+        <v>80</v>
+      </c>
+      <c r="D41" t="s">
+        <v>260</v>
+      </c>
+      <c r="E41" t="s">
+        <v>414</v>
+      </c>
+      <c r="F41">
+        <v>0</v>
+      </c>
+      <c r="G41">
+        <v>16826.9</v>
+      </c>
+      <c r="H41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42">
+        <v>341</v>
+      </c>
+      <c r="B42" t="s">
+        <v>81</v>
+      </c>
+      <c r="C42" t="s">
+        <v>206</v>
+      </c>
+      <c r="D42" t="s">
+        <v>261</v>
+      </c>
+      <c r="E42" t="s">
+        <v>415</v>
+      </c>
+      <c r="F42">
+        <v>0</v>
+      </c>
+      <c r="G42">
+        <v>6810.75</v>
+      </c>
+      <c r="H42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="A43">
+        <v>343</v>
+      </c>
+      <c r="B43" t="s">
+        <v>82</v>
+      </c>
+      <c r="C43" t="s">
+        <v>206</v>
+      </c>
+      <c r="D43" t="s">
+        <v>262</v>
+      </c>
+      <c r="E43" t="s">
+        <v>416</v>
+      </c>
+      <c r="F43">
+        <v>0</v>
+      </c>
+      <c r="G43">
+        <v>7513.35</v>
+      </c>
+      <c r="H43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44">
+        <v>393</v>
+      </c>
+      <c r="B44" t="s">
+        <v>83</v>
+      </c>
+      <c r="C44" t="s">
+        <v>207</v>
+      </c>
+      <c r="D44" t="s">
+        <v>263</v>
+      </c>
+      <c r="E44" t="s">
+        <v>417</v>
+      </c>
+      <c r="F44">
+        <v>0</v>
+      </c>
+      <c r="G44">
+        <v>7531.25</v>
+      </c>
+      <c r="H44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="A45">
+        <v>40</v>
+      </c>
+      <c r="B45" t="s">
+        <v>84</v>
+      </c>
+      <c r="C45" t="s">
+        <v>208</v>
+      </c>
+      <c r="D45" t="s">
+        <v>264</v>
+      </c>
+      <c r="E45" t="s">
+        <v>418</v>
+      </c>
+      <c r="F45">
+        <v>0</v>
+      </c>
+      <c r="G45">
+        <v>11165.6</v>
+      </c>
+      <c r="H45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" t="s">
+        <v>85</v>
+      </c>
+      <c r="C46" t="s">
+        <v>208</v>
+      </c>
+      <c r="D46" t="s">
+        <v>265</v>
+      </c>
+      <c r="E46" t="s">
+        <v>419</v>
+      </c>
+      <c r="F46">
+        <v>0</v>
+      </c>
+      <c r="G46">
+        <v>6976.5</v>
+      </c>
+      <c r="H46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="A47">
+        <v>459</v>
+      </c>
+      <c r="B47" t="s">
+        <v>86</v>
+      </c>
+      <c r="C47" t="s">
+        <v>209</v>
+      </c>
+      <c r="D47" t="s">
+        <v>266</v>
+      </c>
+      <c r="E47" t="s">
+        <v>420</v>
+      </c>
+      <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="G47">
+        <v>9892.299999999999</v>
+      </c>
+      <c r="H47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="A48">
+        <v>46</v>
+      </c>
+      <c r="B48" t="s">
+        <v>87</v>
+      </c>
+      <c r="C48" t="s">
+        <v>208</v>
+      </c>
+      <c r="D48" t="s">
+        <v>267</v>
+      </c>
+      <c r="E48" t="s">
+        <v>421</v>
+      </c>
+      <c r="F48">
+        <v>0</v>
+      </c>
+      <c r="G48">
+        <v>16347.65</v>
+      </c>
+      <c r="H48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
+      <c r="A49">
+        <v>460</v>
+      </c>
+      <c r="B49" t="s">
+        <v>88</v>
+      </c>
+      <c r="C49" t="s">
+        <v>209</v>
+      </c>
+      <c r="D49" t="s">
+        <v>268</v>
+      </c>
+      <c r="E49" t="s">
+        <v>422</v>
+      </c>
+      <c r="F49">
+        <v>0</v>
+      </c>
+      <c r="G49">
+        <v>19248.4</v>
+      </c>
+      <c r="H49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
+      <c r="A50">
+        <v>463</v>
+      </c>
+      <c r="B50" t="s">
+        <v>89</v>
+      </c>
+      <c r="C50" t="s">
+        <v>209</v>
+      </c>
+      <c r="D50" t="s">
+        <v>269</v>
+      </c>
+      <c r="E50" t="s">
+        <v>423</v>
+      </c>
+      <c r="F50">
+        <v>0</v>
+      </c>
+      <c r="G50">
+        <v>11176.95</v>
+      </c>
+      <c r="H50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51">
+        <v>467</v>
+      </c>
+      <c r="B51" t="s">
+        <v>90</v>
+      </c>
+      <c r="C51" t="s">
+        <v>209</v>
+      </c>
+      <c r="D51" t="s">
+        <v>270</v>
+      </c>
+      <c r="E51" t="s">
+        <v>424</v>
+      </c>
+      <c r="F51">
+        <v>0</v>
+      </c>
+      <c r="G51">
+        <v>13586.4</v>
+      </c>
+      <c r="H51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
+      <c r="A52">
+        <v>47</v>
+      </c>
+      <c r="B52" t="s">
+        <v>91</v>
+      </c>
+      <c r="C52" t="s">
+        <v>208</v>
+      </c>
+      <c r="D52" t="s">
+        <v>271</v>
+      </c>
+      <c r="E52" t="s">
+        <v>425</v>
+      </c>
+      <c r="F52">
+        <v>0</v>
+      </c>
+      <c r="G52">
+        <v>10001.25</v>
+      </c>
+      <c r="H52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
+      <c r="A53">
+        <v>470</v>
+      </c>
+      <c r="B53" t="s">
+        <v>92</v>
+      </c>
+      <c r="C53" t="s">
+        <v>209</v>
+      </c>
+      <c r="D53" t="s">
+        <v>272</v>
+      </c>
+      <c r="E53" t="s">
+        <v>426</v>
+      </c>
+      <c r="F53">
+        <v>0</v>
+      </c>
+      <c r="G53">
+        <v>16012.5</v>
+      </c>
+      <c r="H53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
+      <c r="A54">
+        <v>477</v>
+      </c>
+      <c r="B54" t="s">
+        <v>93</v>
+      </c>
+      <c r="C54" t="s">
+        <v>93</v>
+      </c>
+      <c r="D54" t="s">
+        <v>273</v>
+      </c>
+      <c r="E54" t="s">
+        <v>427</v>
+      </c>
+      <c r="F54">
+        <v>0</v>
+      </c>
+      <c r="G54">
+        <v>7492.55</v>
+      </c>
+      <c r="H54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8">
+      <c r="A55">
+        <v>48</v>
+      </c>
+      <c r="B55" t="s">
+        <v>94</v>
+      </c>
+      <c r="C55" t="s">
+        <v>208</v>
+      </c>
+      <c r="D55" t="s">
+        <v>274</v>
+      </c>
+      <c r="E55" t="s">
+        <v>428</v>
+      </c>
+      <c r="F55">
+        <v>0</v>
+      </c>
+      <c r="G55">
+        <v>12908.25</v>
+      </c>
+      <c r="H55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8">
+      <c r="A56">
+        <v>484</v>
+      </c>
+      <c r="B56" t="s">
+        <v>95</v>
+      </c>
+      <c r="C56" t="s">
+        <v>210</v>
+      </c>
+      <c r="D56" t="s">
+        <v>275</v>
+      </c>
+      <c r="E56" t="s">
+        <v>429</v>
+      </c>
+      <c r="F56">
+        <v>0</v>
+      </c>
+      <c r="G56">
+        <v>3637.45</v>
+      </c>
+      <c r="H56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="A57">
+        <v>495</v>
+      </c>
+      <c r="B57" t="s">
+        <v>96</v>
+      </c>
+      <c r="C57" t="s">
+        <v>207</v>
+      </c>
+      <c r="D57" t="s">
+        <v>276</v>
+      </c>
+      <c r="E57" t="s">
+        <v>430</v>
+      </c>
+      <c r="F57">
+        <v>0</v>
+      </c>
+      <c r="G57">
+        <v>10155.05</v>
+      </c>
+      <c r="H57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8">
+      <c r="A58">
+        <v>497</v>
+      </c>
+      <c r="B58" t="s">
+        <v>97</v>
+      </c>
+      <c r="C58" t="s">
+        <v>207</v>
+      </c>
+      <c r="D58" t="s">
+        <v>277</v>
+      </c>
+      <c r="E58" t="s">
+        <v>431</v>
+      </c>
+      <c r="F58">
+        <v>0</v>
+      </c>
+      <c r="G58">
+        <v>1476.05</v>
+      </c>
+      <c r="H58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8">
+      <c r="A59">
+        <v>498</v>
+      </c>
+      <c r="B59" t="s">
+        <v>98</v>
+      </c>
+      <c r="C59" t="s">
+        <v>207</v>
+      </c>
+      <c r="D59" t="s">
+        <v>278</v>
+      </c>
+      <c r="E59" t="s">
+        <v>432</v>
+      </c>
+      <c r="F59">
+        <v>0</v>
+      </c>
+      <c r="G59">
+        <v>1418</v>
+      </c>
+      <c r="H59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8">
+      <c r="A60">
+        <v>499</v>
+      </c>
+      <c r="B60" t="s">
+        <v>99</v>
+      </c>
+      <c r="C60" t="s">
+        <v>207</v>
+      </c>
+      <c r="D60" t="s">
+        <v>278</v>
+      </c>
+      <c r="E60" t="s">
+        <v>432</v>
+      </c>
+      <c r="F60">
+        <v>0</v>
+      </c>
+      <c r="G60">
+        <v>1576.45</v>
+      </c>
+      <c r="H60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8">
+      <c r="A61">
+        <v>5</v>
+      </c>
+      <c r="B61" t="s">
+        <v>100</v>
+      </c>
+      <c r="C61" t="s">
+        <v>201</v>
+      </c>
+      <c r="D61" t="s">
+        <v>279</v>
+      </c>
+      <c r="E61" t="s">
+        <v>433</v>
+      </c>
+      <c r="F61">
+        <v>0</v>
+      </c>
+      <c r="G61">
+        <v>6459.65</v>
+      </c>
+      <c r="H61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8">
+      <c r="A62">
+        <v>500</v>
+      </c>
+      <c r="B62" t="s">
+        <v>101</v>
+      </c>
+      <c r="C62" t="s">
+        <v>207</v>
+      </c>
+      <c r="D62" t="s">
+        <v>280</v>
+      </c>
+      <c r="E62" t="s">
+        <v>434</v>
+      </c>
+      <c r="F62">
+        <v>0</v>
+      </c>
+      <c r="G62">
+        <v>10225.5</v>
+      </c>
+      <c r="H62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8">
+      <c r="A63">
+        <v>511</v>
+      </c>
+      <c r="B63" t="s">
+        <v>102</v>
+      </c>
+      <c r="C63" t="s">
+        <v>207</v>
+      </c>
+      <c r="D63" t="s">
+        <v>281</v>
+      </c>
+      <c r="E63" t="s">
+        <v>435</v>
+      </c>
+      <c r="F63">
+        <v>0</v>
+      </c>
+      <c r="G63">
+        <v>3968.9</v>
+      </c>
+      <c r="H63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8">
+      <c r="A64">
+        <v>512</v>
+      </c>
+      <c r="B64" t="s">
+        <v>103</v>
+      </c>
+      <c r="C64" t="s">
+        <v>207</v>
+      </c>
+      <c r="D64" t="s">
+        <v>282</v>
+      </c>
+      <c r="E64" t="s">
+        <v>436</v>
+      </c>
+      <c r="F64">
+        <v>0</v>
+      </c>
+      <c r="G64">
+        <v>3139.15</v>
+      </c>
+      <c r="H64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8">
+      <c r="A65">
+        <v>514</v>
+      </c>
+      <c r="B65" t="s">
+        <v>104</v>
+      </c>
+      <c r="C65" t="s">
+        <v>207</v>
+      </c>
+      <c r="D65" t="s">
+        <v>283</v>
+      </c>
+      <c r="E65" t="s">
+        <v>437</v>
+      </c>
+      <c r="F65">
+        <v>0</v>
+      </c>
+      <c r="G65">
+        <v>7744.75</v>
+      </c>
+      <c r="H65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8">
+      <c r="A66">
+        <v>517</v>
+      </c>
+      <c r="B66" t="s">
+        <v>105</v>
+      </c>
+      <c r="C66" t="s">
+        <v>207</v>
+      </c>
+      <c r="D66" t="s">
+        <v>277</v>
+      </c>
+      <c r="E66" t="s">
+        <v>431</v>
+      </c>
+      <c r="F66">
+        <v>0</v>
+      </c>
+      <c r="G66">
+        <v>2148.95</v>
+      </c>
+      <c r="H66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8">
+      <c r="A67">
+        <v>519</v>
+      </c>
+      <c r="B67" t="s">
+        <v>106</v>
+      </c>
+      <c r="C67" t="s">
+        <v>211</v>
+      </c>
+      <c r="D67" t="s">
+        <v>284</v>
+      </c>
+      <c r="E67" t="s">
+        <v>438</v>
+      </c>
+      <c r="F67">
+        <v>0</v>
+      </c>
+      <c r="G67">
+        <v>5084.05</v>
+      </c>
+      <c r="H67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8">
+      <c r="A68">
+        <v>52</v>
+      </c>
+      <c r="B68" t="s">
+        <v>107</v>
+      </c>
+      <c r="C68" t="s">
+        <v>208</v>
+      </c>
+      <c r="D68" t="s">
+        <v>285</v>
+      </c>
+      <c r="E68" t="s">
+        <v>439</v>
+      </c>
+      <c r="F68">
+        <v>0</v>
+      </c>
+      <c r="G68">
+        <v>7457.3</v>
+      </c>
+      <c r="H68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8">
+      <c r="A69">
+        <v>520</v>
+      </c>
+      <c r="B69" t="s">
+        <v>108</v>
+      </c>
+      <c r="C69" t="s">
+        <v>211</v>
+      </c>
+      <c r="D69" t="s">
+        <v>286</v>
+      </c>
+      <c r="E69" t="s">
+        <v>440</v>
+      </c>
+      <c r="F69">
+        <v>0</v>
+      </c>
+      <c r="G69">
+        <v>6374.05</v>
+      </c>
+      <c r="H69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8">
+      <c r="A70">
+        <v>521</v>
+      </c>
+      <c r="B70" t="s">
+        <v>109</v>
+      </c>
+      <c r="C70" t="s">
+        <v>212</v>
+      </c>
+      <c r="D70" t="s">
+        <v>287</v>
+      </c>
+      <c r="E70" t="s">
+        <v>441</v>
+      </c>
+      <c r="F70">
+        <v>0</v>
+      </c>
+      <c r="G70">
+        <v>6844.3</v>
+      </c>
+      <c r="H70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8">
+      <c r="A71">
+        <v>522</v>
+      </c>
+      <c r="B71" t="s">
+        <v>110</v>
+      </c>
+      <c r="C71" t="s">
+        <v>212</v>
+      </c>
+      <c r="D71" t="s">
+        <v>288</v>
+      </c>
+      <c r="E71" t="s">
+        <v>442</v>
+      </c>
+      <c r="F71">
+        <v>0</v>
+      </c>
+      <c r="G71">
+        <v>11958.7</v>
+      </c>
+      <c r="H71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8">
+      <c r="A72">
+        <v>523</v>
+      </c>
+      <c r="B72" t="s">
+        <v>111</v>
+      </c>
+      <c r="C72" t="s">
+        <v>212</v>
+      </c>
+      <c r="D72" t="s">
+        <v>289</v>
+      </c>
+      <c r="E72" t="s">
+        <v>443</v>
+      </c>
+      <c r="F72">
+        <v>0</v>
+      </c>
+      <c r="G72">
+        <v>15756.8</v>
+      </c>
+      <c r="H72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8">
+      <c r="A73">
+        <v>524</v>
+      </c>
+      <c r="B73" t="s">
+        <v>112</v>
+      </c>
+      <c r="C73" t="s">
+        <v>212</v>
+      </c>
+      <c r="D73" t="s">
+        <v>290</v>
+      </c>
+      <c r="E73" t="s">
+        <v>444</v>
+      </c>
+      <c r="F73">
+        <v>0</v>
+      </c>
+      <c r="G73">
+        <v>9146.299999999999</v>
+      </c>
+      <c r="H73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8">
+      <c r="A74">
+        <v>529</v>
+      </c>
+      <c r="B74" t="s">
+        <v>113</v>
+      </c>
+      <c r="C74" t="s">
+        <v>93</v>
+      </c>
+      <c r="D74" t="s">
+        <v>291</v>
+      </c>
+      <c r="E74" t="s">
+        <v>445</v>
+      </c>
+      <c r="F74">
+        <v>0</v>
+      </c>
+      <c r="G74">
+        <v>5858.3</v>
+      </c>
+      <c r="H74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8">
+      <c r="A75">
+        <v>531</v>
+      </c>
+      <c r="B75" t="s">
+        <v>114</v>
+      </c>
+      <c r="C75" t="s">
+        <v>210</v>
+      </c>
+      <c r="D75" t="s">
+        <v>292</v>
+      </c>
+      <c r="E75" t="s">
+        <v>446</v>
+      </c>
+      <c r="F75">
+        <v>0</v>
+      </c>
+      <c r="G75">
+        <v>15072.55</v>
+      </c>
+      <c r="H75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8">
+      <c r="A76">
+        <v>532</v>
+      </c>
+      <c r="B76" t="s">
+        <v>115</v>
+      </c>
+      <c r="C76" t="s">
+        <v>210</v>
+      </c>
+      <c r="D76" t="s">
+        <v>293</v>
+      </c>
+      <c r="E76" t="s">
+        <v>447</v>
+      </c>
+      <c r="F76">
+        <v>0</v>
+      </c>
+      <c r="G76">
+        <v>7247.2</v>
+      </c>
+      <c r="H76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8">
+      <c r="A77">
         <v>533</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B77" t="s">
+        <v>116</v>
+      </c>
+      <c r="C77" t="s">
+        <v>210</v>
+      </c>
+      <c r="D77" t="s">
+        <v>294</v>
+      </c>
+      <c r="E77" t="s">
+        <v>448</v>
+      </c>
+      <c r="F77">
+        <v>2</v>
+      </c>
+      <c r="G77">
+        <v>10752.5</v>
+      </c>
+      <c r="H77">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8">
+      <c r="A78">
+        <v>534</v>
+      </c>
+      <c r="B78" t="s">
+        <v>117</v>
+      </c>
+      <c r="C78" t="s">
+        <v>210</v>
+      </c>
+      <c r="D78" t="s">
+        <v>295</v>
+      </c>
+      <c r="E78" t="s">
+        <v>449</v>
+      </c>
+      <c r="F78">
+        <v>0</v>
+      </c>
+      <c r="G78">
+        <v>3585.05</v>
+      </c>
+      <c r="H78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8">
+      <c r="A79">
+        <v>535</v>
+      </c>
+      <c r="B79" t="s">
+        <v>118</v>
+      </c>
+      <c r="C79" t="s">
+        <v>210</v>
+      </c>
+      <c r="D79" t="s">
+        <v>296</v>
+      </c>
+      <c r="E79" t="s">
+        <v>450</v>
+      </c>
+      <c r="F79">
+        <v>0</v>
+      </c>
+      <c r="G79">
+        <v>5808.5</v>
+      </c>
+      <c r="H79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8">
+      <c r="A80">
+        <v>536</v>
+      </c>
+      <c r="B80" t="s">
+        <v>119</v>
+      </c>
+      <c r="C80" t="s">
+        <v>210</v>
+      </c>
+      <c r="D80" t="s">
+        <v>297</v>
+      </c>
+      <c r="E80" t="s">
+        <v>451</v>
+      </c>
+      <c r="F80">
+        <v>0</v>
+      </c>
+      <c r="G80">
+        <v>5091.1</v>
+      </c>
+      <c r="H80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8">
+      <c r="A81">
+        <v>548</v>
+      </c>
+      <c r="B81" t="s">
+        <v>120</v>
+      </c>
+      <c r="C81" t="s">
+        <v>213</v>
+      </c>
+      <c r="D81" t="s">
+        <v>298</v>
+      </c>
+      <c r="E81" t="s">
+        <v>452</v>
+      </c>
+      <c r="F81">
+        <v>0</v>
+      </c>
+      <c r="G81">
+        <v>8739.799999999999</v>
+      </c>
+      <c r="H81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8">
+      <c r="A82">
+        <v>549</v>
+      </c>
+      <c r="B82" t="s">
+        <v>121</v>
+      </c>
+      <c r="C82" t="s">
+        <v>213</v>
+      </c>
+      <c r="D82" t="s">
+        <v>299</v>
+      </c>
+      <c r="E82" t="s">
+        <v>453</v>
+      </c>
+      <c r="F82">
+        <v>0</v>
+      </c>
+      <c r="G82">
+        <v>23731.85</v>
+      </c>
+      <c r="H82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8">
+      <c r="A83">
+        <v>550</v>
+      </c>
+      <c r="B83" t="s">
+        <v>122</v>
+      </c>
+      <c r="C83" t="s">
+        <v>213</v>
+      </c>
+      <c r="D83" t="s">
+        <v>300</v>
+      </c>
+      <c r="E83" t="s">
+        <v>454</v>
+      </c>
+      <c r="F83">
+        <v>0</v>
+      </c>
+      <c r="G83">
+        <v>11989.45</v>
+      </c>
+      <c r="H83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8">
+      <c r="A84">
+        <v>557</v>
+      </c>
+      <c r="B84" t="s">
+        <v>123</v>
+      </c>
+      <c r="C84" t="s">
+        <v>208</v>
+      </c>
+      <c r="D84" t="s">
+        <v>301</v>
+      </c>
+      <c r="E84" t="s">
+        <v>455</v>
+      </c>
+      <c r="F84">
+        <v>0</v>
+      </c>
+      <c r="G84">
+        <v>11384.4</v>
+      </c>
+      <c r="H84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8">
+      <c r="A85">
+        <v>56</v>
+      </c>
+      <c r="B85" t="s">
+        <v>124</v>
+      </c>
+      <c r="C85" t="s">
+        <v>214</v>
+      </c>
+      <c r="D85" t="s">
+        <v>302</v>
+      </c>
+      <c r="E85" t="s">
+        <v>456</v>
+      </c>
+      <c r="F85">
+        <v>0</v>
+      </c>
+      <c r="G85">
+        <v>14049.1</v>
+      </c>
+      <c r="H85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8">
+      <c r="A86">
+        <v>562</v>
+      </c>
+      <c r="B86" t="s">
+        <v>125</v>
+      </c>
+      <c r="C86" t="s">
+        <v>211</v>
+      </c>
+      <c r="D86" t="s">
+        <v>303</v>
+      </c>
+      <c r="E86" t="s">
+        <v>457</v>
+      </c>
+      <c r="F86">
+        <v>0</v>
+      </c>
+      <c r="G86">
+        <v>3820.15</v>
+      </c>
+      <c r="H86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8">
+      <c r="A87">
+        <v>564</v>
+      </c>
+      <c r="B87" t="s">
+        <v>126</v>
+      </c>
+      <c r="C87" t="s">
+        <v>80</v>
+      </c>
+      <c r="D87" t="s">
+        <v>304</v>
+      </c>
+      <c r="E87" t="s">
+        <v>458</v>
+      </c>
+      <c r="F87">
+        <v>0</v>
+      </c>
+      <c r="G87">
+        <v>3588.95</v>
+      </c>
+      <c r="H87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8">
+      <c r="A88">
+        <v>566</v>
+      </c>
+      <c r="B88" t="s">
+        <v>127</v>
+      </c>
+      <c r="C88" t="s">
+        <v>163</v>
+      </c>
+      <c r="D88" t="s">
+        <v>305</v>
+      </c>
+      <c r="E88" t="s">
+        <v>459</v>
+      </c>
+      <c r="F88">
+        <v>0</v>
+      </c>
+      <c r="G88">
+        <v>5411.8</v>
+      </c>
+      <c r="H88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8">
+      <c r="A89">
+        <v>57</v>
+      </c>
+      <c r="B89" t="s">
+        <v>128</v>
+      </c>
+      <c r="C89" t="s">
+        <v>214</v>
+      </c>
+      <c r="D89" t="s">
+        <v>306</v>
+      </c>
+      <c r="E89" t="s">
+        <v>460</v>
+      </c>
+      <c r="F89">
+        <v>0</v>
+      </c>
+      <c r="G89">
+        <v>13637.95</v>
+      </c>
+      <c r="H89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8">
+      <c r="A90">
+        <v>58</v>
+      </c>
+      <c r="B90" t="s">
+        <v>129</v>
+      </c>
+      <c r="C90" t="s">
+        <v>214</v>
+      </c>
+      <c r="D90" t="s">
+        <v>307</v>
+      </c>
+      <c r="E90" t="s">
+        <v>461</v>
+      </c>
+      <c r="F90">
+        <v>0</v>
+      </c>
+      <c r="G90">
+        <v>12879.25</v>
+      </c>
+      <c r="H90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8">
+      <c r="A91">
+        <v>605</v>
+      </c>
+      <c r="B91" t="s">
+        <v>130</v>
+      </c>
+      <c r="C91" t="s">
+        <v>93</v>
+      </c>
+      <c r="D91" t="s">
+        <v>308</v>
+      </c>
+      <c r="E91" t="s">
+        <v>462</v>
+      </c>
+      <c r="F91">
+        <v>0</v>
+      </c>
+      <c r="G91">
+        <v>6823.6</v>
+      </c>
+      <c r="H91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8">
+      <c r="A92">
+        <v>61</v>
+      </c>
+      <c r="B92" t="s">
+        <v>131</v>
+      </c>
+      <c r="C92" t="s">
+        <v>214</v>
+      </c>
+      <c r="D92" t="s">
+        <v>309</v>
+      </c>
+      <c r="E92" t="s">
+        <v>463</v>
+      </c>
+      <c r="F92">
+        <v>0</v>
+      </c>
+      <c r="G92">
+        <v>15084.4</v>
+      </c>
+      <c r="H92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8">
+      <c r="A93">
+        <v>631</v>
+      </c>
+      <c r="B93" t="s">
+        <v>132</v>
+      </c>
+      <c r="C93" t="s">
+        <v>202</v>
+      </c>
+      <c r="D93" t="s">
+        <v>310</v>
+      </c>
+      <c r="E93" t="s">
+        <v>464</v>
+      </c>
+      <c r="F93">
+        <v>0</v>
+      </c>
+      <c r="G93">
+        <v>4640.5</v>
+      </c>
+      <c r="H93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8">
+      <c r="A94">
+        <v>645</v>
+      </c>
+      <c r="B94" t="s">
+        <v>133</v>
+      </c>
+      <c r="C94" t="s">
+        <v>215</v>
+      </c>
+      <c r="D94" t="s">
+        <v>311</v>
+      </c>
+      <c r="E94" t="s">
+        <v>465</v>
+      </c>
+      <c r="F94">
+        <v>0</v>
+      </c>
+      <c r="G94">
+        <v>10507.05</v>
+      </c>
+      <c r="H94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8">
+      <c r="A95">
+        <v>646</v>
+      </c>
+      <c r="B95" t="s">
+        <v>134</v>
+      </c>
+      <c r="C95" t="s">
+        <v>215</v>
+      </c>
+      <c r="D95" t="s">
+        <v>312</v>
+      </c>
+      <c r="E95" t="s">
+        <v>466</v>
+      </c>
+      <c r="F95">
+        <v>0</v>
+      </c>
+      <c r="G95">
+        <v>16131.2</v>
+      </c>
+      <c r="H95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8">
+      <c r="A96">
+        <v>647</v>
+      </c>
+      <c r="B96" t="s">
+        <v>135</v>
+      </c>
+      <c r="C96" t="s">
+        <v>215</v>
+      </c>
+      <c r="D96" t="s">
+        <v>313</v>
+      </c>
+      <c r="E96" t="s">
+        <v>467</v>
+      </c>
+      <c r="F96">
+        <v>0</v>
+      </c>
+      <c r="G96">
+        <v>6401.05</v>
+      </c>
+      <c r="H96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8">
+      <c r="A97">
+        <v>651</v>
+      </c>
+      <c r="B97" t="s">
+        <v>136</v>
+      </c>
+      <c r="C97" t="s">
+        <v>214</v>
+      </c>
+      <c r="D97" t="s">
+        <v>314</v>
+      </c>
+      <c r="E97" t="s">
+        <v>468</v>
+      </c>
+      <c r="F97">
+        <v>0</v>
+      </c>
+      <c r="G97">
+        <v>13661.55</v>
+      </c>
+      <c r="H97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8">
+      <c r="A98">
+        <v>653</v>
+      </c>
+      <c r="B98" t="s">
+        <v>137</v>
+      </c>
+      <c r="C98" t="s">
+        <v>213</v>
+      </c>
+      <c r="D98" t="s">
+        <v>315</v>
+      </c>
+      <c r="E98" t="s">
+        <v>469</v>
+      </c>
+      <c r="F98">
+        <v>0</v>
+      </c>
+      <c r="G98">
+        <v>8831</v>
+      </c>
+      <c r="H98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8">
+      <c r="A99">
+        <v>677</v>
+      </c>
+      <c r="B99" t="s">
+        <v>138</v>
+      </c>
+      <c r="C99" t="s">
+        <v>212</v>
+      </c>
+      <c r="D99" t="s">
+        <v>316</v>
+      </c>
+      <c r="E99" t="s">
+        <v>470</v>
+      </c>
+      <c r="F99">
+        <v>0</v>
+      </c>
+      <c r="G99">
+        <v>3160.55</v>
+      </c>
+      <c r="H99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8">
+      <c r="A100">
+        <v>688</v>
+      </c>
+      <c r="B100" t="s">
+        <v>139</v>
+      </c>
+      <c r="C100" t="s">
+        <v>205</v>
+      </c>
+      <c r="D100" t="s">
+        <v>317</v>
+      </c>
+      <c r="E100" t="s">
+        <v>471</v>
+      </c>
+      <c r="F100">
+        <v>0</v>
+      </c>
+      <c r="G100">
+        <v>5385.2</v>
+      </c>
+      <c r="H100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8">
+      <c r="A101">
+        <v>70</v>
+      </c>
+      <c r="B101" t="s">
+        <v>140</v>
+      </c>
+      <c r="C101" t="s">
+        <v>214</v>
+      </c>
+      <c r="D101" t="s">
+        <v>318</v>
+      </c>
+      <c r="E101" t="s">
+        <v>472</v>
+      </c>
+      <c r="F101">
+        <v>0</v>
+      </c>
+      <c r="G101">
+        <v>15864.35</v>
+      </c>
+      <c r="H101">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8">
+      <c r="A102">
+        <v>700</v>
+      </c>
+      <c r="B102" t="s">
+        <v>141</v>
+      </c>
+      <c r="C102" t="s">
+        <v>213</v>
+      </c>
+      <c r="D102" t="s">
+        <v>319</v>
+      </c>
+      <c r="E102" t="s">
+        <v>473</v>
+      </c>
+      <c r="F102">
+        <v>0</v>
+      </c>
+      <c r="G102">
+        <v>11644.1</v>
+      </c>
+      <c r="H102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8">
+      <c r="A103">
+        <v>721</v>
+      </c>
+      <c r="B103" t="s">
+        <v>142</v>
+      </c>
+      <c r="C103" t="s">
+        <v>211</v>
+      </c>
+      <c r="D103" t="s">
+        <v>320</v>
+      </c>
+      <c r="E103" t="s">
+        <v>474</v>
+      </c>
+      <c r="F103">
+        <v>0</v>
+      </c>
+      <c r="G103">
+        <v>5345.1</v>
+      </c>
+      <c r="H103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8">
+      <c r="A104">
+        <v>73</v>
+      </c>
+      <c r="B104" t="s">
+        <v>143</v>
+      </c>
+      <c r="C104" t="s">
+        <v>214</v>
+      </c>
+      <c r="D104" t="s">
+        <v>321</v>
+      </c>
+      <c r="E104" t="s">
+        <v>475</v>
+      </c>
+      <c r="F104">
+        <v>0</v>
+      </c>
+      <c r="G104">
+        <v>10058.4</v>
+      </c>
+      <c r="H104">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8">
+      <c r="A105">
+        <v>79</v>
+      </c>
+      <c r="B105" t="s">
+        <v>144</v>
+      </c>
+      <c r="C105" t="s">
+        <v>216</v>
+      </c>
+      <c r="D105" t="s">
+        <v>322</v>
+      </c>
+      <c r="E105" t="s">
+        <v>476</v>
+      </c>
+      <c r="F105">
+        <v>0</v>
+      </c>
+      <c r="G105">
+        <v>18172.95</v>
+      </c>
+      <c r="H105">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8">
+      <c r="A106">
+        <v>80</v>
+      </c>
+      <c r="B106" t="s">
+        <v>145</v>
+      </c>
+      <c r="C106" t="s">
+        <v>216</v>
+      </c>
+      <c r="D106" t="s">
+        <v>323</v>
+      </c>
+      <c r="E106" t="s">
+        <v>477</v>
+      </c>
+      <c r="F106">
+        <v>0</v>
+      </c>
+      <c r="G106">
+        <v>13687.8</v>
+      </c>
+      <c r="H106">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8">
+      <c r="A107">
+        <v>81</v>
+      </c>
+      <c r="B107" t="s">
+        <v>146</v>
+      </c>
+      <c r="C107" t="s">
+        <v>216</v>
+      </c>
+      <c r="D107" t="s">
+        <v>324</v>
+      </c>
+      <c r="E107" t="s">
+        <v>478</v>
+      </c>
+      <c r="F107">
+        <v>0</v>
+      </c>
+      <c r="G107">
+        <v>11744.1</v>
+      </c>
+      <c r="H107">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8">
+      <c r="A108">
+        <v>84</v>
+      </c>
+      <c r="B108" t="s">
+        <v>147</v>
+      </c>
+      <c r="C108" t="s">
+        <v>216</v>
+      </c>
+      <c r="D108" t="s">
+        <v>325</v>
+      </c>
+      <c r="E108" t="s">
+        <v>479</v>
+      </c>
+      <c r="F108">
+        <v>0</v>
+      </c>
+      <c r="G108">
+        <v>9983.049999999999</v>
+      </c>
+      <c r="H108">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8">
+      <c r="A109">
+        <v>843</v>
+      </c>
+      <c r="B109" t="s">
+        <v>148</v>
+      </c>
+      <c r="C109" t="s">
+        <v>211</v>
+      </c>
+      <c r="D109" t="s">
+        <v>284</v>
+      </c>
+      <c r="E109" t="s">
+        <v>438</v>
+      </c>
+      <c r="F109">
+        <v>0</v>
+      </c>
+      <c r="G109">
+        <v>5867</v>
+      </c>
+      <c r="H109">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8">
+      <c r="A110">
+        <v>85</v>
+      </c>
+      <c r="B110" t="s">
+        <v>149</v>
+      </c>
+      <c r="C110" t="s">
+        <v>216</v>
+      </c>
+      <c r="D110" t="s">
+        <v>326</v>
+      </c>
+      <c r="E110" t="s">
+        <v>480</v>
+      </c>
+      <c r="F110">
+        <v>0</v>
+      </c>
+      <c r="G110">
+        <v>7482.35</v>
+      </c>
+      <c r="H110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8">
+      <c r="A111">
+        <v>850</v>
+      </c>
+      <c r="B111" t="s">
+        <v>150</v>
+      </c>
+      <c r="C111" t="s">
+        <v>211</v>
+      </c>
+      <c r="D111" t="s">
+        <v>327</v>
+      </c>
+      <c r="E111" t="s">
+        <v>481</v>
+      </c>
+      <c r="F111">
+        <v>0</v>
+      </c>
+      <c r="G111">
+        <v>4270.45</v>
+      </c>
+      <c r="H111">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8">
+      <c r="A112">
+        <v>857</v>
+      </c>
+      <c r="B112" t="s">
+        <v>151</v>
+      </c>
+      <c r="C112" t="s">
+        <v>200</v>
+      </c>
+      <c r="D112" t="s">
+        <v>328</v>
+      </c>
+      <c r="E112" t="s">
+        <v>482</v>
+      </c>
+      <c r="F112">
+        <v>0</v>
+      </c>
+      <c r="G112">
+        <v>4323.95</v>
+      </c>
+      <c r="H112">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8">
+      <c r="A113">
+        <v>858</v>
+      </c>
+      <c r="B113" t="s">
+        <v>152</v>
+      </c>
+      <c r="C113" t="s">
+        <v>200</v>
+      </c>
+      <c r="D113" t="s">
+        <v>329</v>
+      </c>
+      <c r="E113" t="s">
+        <v>483</v>
+      </c>
+      <c r="F113">
+        <v>0</v>
+      </c>
+      <c r="G113">
+        <v>21082.3</v>
+      </c>
+      <c r="H113">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8">
+      <c r="A114">
+        <v>86</v>
+      </c>
+      <c r="B114" t="s">
+        <v>153</v>
+      </c>
+      <c r="C114" t="s">
+        <v>216</v>
+      </c>
+      <c r="D114" t="s">
+        <v>330</v>
+      </c>
+      <c r="E114" t="s">
+        <v>484</v>
+      </c>
+      <c r="F114">
+        <v>0</v>
+      </c>
+      <c r="G114">
+        <v>22628.3</v>
+      </c>
+      <c r="H114">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8">
+      <c r="A115">
+        <v>867</v>
+      </c>
+      <c r="B115" t="s">
+        <v>154</v>
+      </c>
+      <c r="C115" t="s">
+        <v>200</v>
+      </c>
+      <c r="D115" t="s">
+        <v>331</v>
+      </c>
+      <c r="E115" t="s">
+        <v>485</v>
+      </c>
+      <c r="F115">
+        <v>0</v>
+      </c>
+      <c r="G115">
+        <v>3020.6</v>
+      </c>
+      <c r="H115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8">
+      <c r="A116">
+        <v>87</v>
+      </c>
+      <c r="B116" t="s">
+        <v>155</v>
+      </c>
+      <c r="C116" t="s">
+        <v>216</v>
+      </c>
+      <c r="D116" t="s">
+        <v>332</v>
+      </c>
+      <c r="E116" t="s">
+        <v>486</v>
+      </c>
+      <c r="F116">
+        <v>0</v>
+      </c>
+      <c r="G116">
+        <v>8496.85</v>
+      </c>
+      <c r="H116">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8">
+      <c r="A117">
+        <v>876</v>
+      </c>
+      <c r="B117" t="s">
+        <v>156</v>
+      </c>
+      <c r="C117" t="s">
+        <v>208</v>
+      </c>
+      <c r="D117" t="s">
+        <v>333</v>
+      </c>
+      <c r="E117" t="s">
+        <v>487</v>
+      </c>
+      <c r="F117">
+        <v>0</v>
+      </c>
+      <c r="G117">
+        <v>6806.85</v>
+      </c>
+      <c r="H117">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8">
+      <c r="A118">
+        <v>877</v>
+      </c>
+      <c r="B118" t="s">
+        <v>157</v>
+      </c>
+      <c r="C118" t="s">
+        <v>208</v>
+      </c>
+      <c r="D118" t="s">
+        <v>334</v>
+      </c>
+      <c r="E118" t="s">
+        <v>488</v>
+      </c>
+      <c r="F118">
+        <v>0</v>
+      </c>
+      <c r="G118">
+        <v>8414.35</v>
+      </c>
+      <c r="H118">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8">
+      <c r="A119">
+        <v>88</v>
+      </c>
+      <c r="B119" t="s">
+        <v>158</v>
+      </c>
+      <c r="C119" t="s">
+        <v>216</v>
+      </c>
+      <c r="D119" t="s">
+        <v>335</v>
+      </c>
+      <c r="E119" t="s">
+        <v>489</v>
+      </c>
+      <c r="F119">
+        <v>0</v>
+      </c>
+      <c r="G119">
+        <v>1787.8</v>
+      </c>
+      <c r="H119">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8">
+      <c r="A120">
+        <v>89</v>
+      </c>
+      <c r="B120" t="s">
+        <v>159</v>
+      </c>
+      <c r="C120" t="s">
+        <v>216</v>
+      </c>
+      <c r="D120" t="s">
+        <v>336</v>
+      </c>
+      <c r="E120" t="s">
+        <v>490</v>
+      </c>
+      <c r="F120">
+        <v>0</v>
+      </c>
+      <c r="G120">
+        <v>9438.15</v>
+      </c>
+      <c r="H120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8">
+      <c r="A121">
+        <v>907</v>
+      </c>
+      <c r="B121" t="s">
+        <v>160</v>
+      </c>
+      <c r="C121" t="s">
+        <v>163</v>
+      </c>
+      <c r="D121" t="s">
+        <v>337</v>
+      </c>
+      <c r="E121" t="s">
+        <v>491</v>
+      </c>
+      <c r="F121">
+        <v>0</v>
+      </c>
+      <c r="G121">
+        <v>8256.75</v>
+      </c>
+      <c r="H121">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8">
+      <c r="A122">
+        <v>923</v>
+      </c>
+      <c r="B122" t="s">
+        <v>161</v>
+      </c>
+      <c r="C122" t="s">
+        <v>93</v>
+      </c>
+      <c r="D122" t="s">
+        <v>338</v>
+      </c>
+      <c r="E122" t="s">
+        <v>492</v>
+      </c>
+      <c r="F122">
+        <v>0</v>
+      </c>
+      <c r="G122">
+        <v>2352.4</v>
+      </c>
+      <c r="H122">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8">
+      <c r="A123">
+        <v>93</v>
+      </c>
+      <c r="B123" t="s">
+        <v>162</v>
+      </c>
+      <c r="C123" t="s">
+        <v>163</v>
+      </c>
+      <c r="D123" t="s">
+        <v>339</v>
+      </c>
+      <c r="E123" t="s">
+        <v>493</v>
+      </c>
+      <c r="F123">
+        <v>0</v>
+      </c>
+      <c r="G123">
+        <v>10029.85</v>
+      </c>
+      <c r="H123">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8">
+      <c r="A124">
+        <v>94</v>
+      </c>
+      <c r="B124" t="s">
+        <v>163</v>
+      </c>
+      <c r="C124" t="s">
+        <v>163</v>
+      </c>
+      <c r="D124" t="s">
+        <v>340</v>
+      </c>
+      <c r="E124" t="s">
+        <v>494</v>
+      </c>
+      <c r="F124">
+        <v>0</v>
+      </c>
+      <c r="G124">
+        <v>15916.8</v>
+      </c>
+      <c r="H124">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8">
+      <c r="A125">
+        <v>97</v>
+      </c>
+      <c r="B125" t="s">
+        <v>164</v>
+      </c>
+      <c r="C125" t="s">
+        <v>163</v>
+      </c>
+      <c r="D125" t="s">
+        <v>341</v>
+      </c>
+      <c r="E125" t="s">
+        <v>495</v>
+      </c>
+      <c r="F125">
+        <v>0</v>
+      </c>
+      <c r="G125">
+        <v>9292.5</v>
+      </c>
+      <c r="H125">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8">
+      <c r="A126">
+        <v>99</v>
+      </c>
+      <c r="B126" t="s">
+        <v>165</v>
+      </c>
+      <c r="C126" t="s">
+        <v>163</v>
+      </c>
+      <c r="D126" t="s">
+        <v>342</v>
+      </c>
+      <c r="E126" t="s">
+        <v>496</v>
+      </c>
+      <c r="F126">
+        <v>0</v>
+      </c>
+      <c r="G126">
+        <v>3170.55</v>
+      </c>
+      <c r="H126">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8">
+      <c r="A127" t="s">
         <v>8</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B127" t="s">
+        <v>166</v>
+      </c>
+      <c r="C127" t="s">
+        <v>217</v>
+      </c>
+      <c r="D127" t="s">
+        <v>343</v>
+      </c>
+      <c r="E127" t="s">
+        <v>497</v>
+      </c>
+      <c r="F127">
+        <v>0</v>
+      </c>
+      <c r="G127">
+        <v>9672.299999999999</v>
+      </c>
+      <c r="H127">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8">
+      <c r="A128" t="s">
         <v>9</v>
       </c>
-      <c r="D2" t="s">
+      <c r="B128" t="s">
+        <v>167</v>
+      </c>
+      <c r="C128" t="s">
+        <v>217</v>
+      </c>
+      <c r="D128" t="s">
+        <v>344</v>
+      </c>
+      <c r="E128" t="s">
+        <v>498</v>
+      </c>
+      <c r="F128">
+        <v>0</v>
+      </c>
+      <c r="G128">
+        <v>12818.55</v>
+      </c>
+      <c r="H128">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8">
+      <c r="A129" t="s">
         <v>10</v>
       </c>
-      <c r="E2" t="s">
+      <c r="B129" t="s">
+        <v>168</v>
+      </c>
+      <c r="C129" t="s">
+        <v>217</v>
+      </c>
+      <c r="D129" t="s">
+        <v>345</v>
+      </c>
+      <c r="E129" t="s">
+        <v>499</v>
+      </c>
+      <c r="F129">
+        <v>0</v>
+      </c>
+      <c r="G129">
+        <v>14398.9</v>
+      </c>
+      <c r="H129">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8">
+      <c r="A130" t="s">
         <v>11</v>
       </c>
-      <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="G2">
-        <v>517.15</v>
-      </c>
-      <c r="H2">
-        <v>2</v>
+      <c r="B130" t="s">
+        <v>169</v>
+      </c>
+      <c r="C130" t="s">
+        <v>217</v>
+      </c>
+      <c r="D130" t="s">
+        <v>346</v>
+      </c>
+      <c r="E130" t="s">
+        <v>500</v>
+      </c>
+      <c r="F130">
+        <v>0</v>
+      </c>
+      <c r="G130">
+        <v>16610.85</v>
+      </c>
+      <c r="H130">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8">
+      <c r="A131" t="s">
+        <v>12</v>
+      </c>
+      <c r="B131" t="s">
+        <v>170</v>
+      </c>
+      <c r="C131" t="s">
+        <v>217</v>
+      </c>
+      <c r="D131" t="s">
+        <v>347</v>
+      </c>
+      <c r="E131" t="s">
+        <v>501</v>
+      </c>
+      <c r="F131">
+        <v>0</v>
+      </c>
+      <c r="G131">
+        <v>6226.05</v>
+      </c>
+      <c r="H131">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8">
+      <c r="A132" t="s">
+        <v>13</v>
+      </c>
+      <c r="B132" t="s">
+        <v>171</v>
+      </c>
+      <c r="C132" t="s">
+        <v>218</v>
+      </c>
+      <c r="D132" t="s">
+        <v>348</v>
+      </c>
+      <c r="E132" t="s">
+        <v>502</v>
+      </c>
+      <c r="F132">
+        <v>0</v>
+      </c>
+      <c r="G132">
+        <v>6941.05</v>
+      </c>
+      <c r="H132">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8">
+      <c r="A133" t="s">
+        <v>14</v>
+      </c>
+      <c r="B133" t="s">
+        <v>172</v>
+      </c>
+      <c r="C133" t="s">
+        <v>218</v>
+      </c>
+      <c r="D133" t="s">
+        <v>349</v>
+      </c>
+      <c r="E133" t="s">
+        <v>503</v>
+      </c>
+      <c r="F133">
+        <v>0</v>
+      </c>
+      <c r="G133">
+        <v>9722.450000000001</v>
+      </c>
+      <c r="H133">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8">
+      <c r="A134" t="s">
+        <v>15</v>
+      </c>
+      <c r="B134" t="s">
+        <v>173</v>
+      </c>
+      <c r="C134" t="s">
+        <v>218</v>
+      </c>
+      <c r="D134" t="s">
+        <v>350</v>
+      </c>
+      <c r="E134" t="s">
+        <v>504</v>
+      </c>
+      <c r="F134">
+        <v>0</v>
+      </c>
+      <c r="G134">
+        <v>9879.549999999999</v>
+      </c>
+      <c r="H134">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8">
+      <c r="A135" t="s">
+        <v>16</v>
+      </c>
+      <c r="B135" t="s">
+        <v>174</v>
+      </c>
+      <c r="C135" t="s">
+        <v>218</v>
+      </c>
+      <c r="D135" t="s">
+        <v>351</v>
+      </c>
+      <c r="E135" t="s">
+        <v>505</v>
+      </c>
+      <c r="F135">
+        <v>0</v>
+      </c>
+      <c r="G135">
+        <v>8889.85</v>
+      </c>
+      <c r="H135">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8">
+      <c r="A136" t="s">
+        <v>17</v>
+      </c>
+      <c r="B136" t="s">
+        <v>175</v>
+      </c>
+      <c r="C136" t="s">
+        <v>218</v>
+      </c>
+      <c r="D136" t="s">
+        <v>352</v>
+      </c>
+      <c r="E136" t="s">
+        <v>506</v>
+      </c>
+      <c r="F136">
+        <v>0</v>
+      </c>
+      <c r="G136">
+        <v>7063.35</v>
+      </c>
+      <c r="H136">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8">
+      <c r="A137" t="s">
+        <v>18</v>
+      </c>
+      <c r="B137" t="s">
+        <v>176</v>
+      </c>
+      <c r="C137" t="s">
+        <v>219</v>
+      </c>
+      <c r="D137" t="s">
+        <v>353</v>
+      </c>
+      <c r="E137" t="s">
+        <v>507</v>
+      </c>
+      <c r="F137">
+        <v>0</v>
+      </c>
+      <c r="G137">
+        <v>4801.95</v>
+      </c>
+      <c r="H137">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8">
+      <c r="A138" t="s">
+        <v>19</v>
+      </c>
+      <c r="B138" t="s">
+        <v>177</v>
+      </c>
+      <c r="C138" t="s">
+        <v>219</v>
+      </c>
+      <c r="D138" t="s">
+        <v>354</v>
+      </c>
+      <c r="E138" t="s">
+        <v>508</v>
+      </c>
+      <c r="F138">
+        <v>0</v>
+      </c>
+      <c r="G138">
+        <v>12195.15</v>
+      </c>
+      <c r="H138">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8">
+      <c r="A139" t="s">
+        <v>20</v>
+      </c>
+      <c r="B139" t="s">
+        <v>178</v>
+      </c>
+      <c r="C139" t="s">
+        <v>219</v>
+      </c>
+      <c r="D139" t="s">
+        <v>355</v>
+      </c>
+      <c r="E139" t="s">
+        <v>509</v>
+      </c>
+      <c r="F139">
+        <v>0</v>
+      </c>
+      <c r="G139">
+        <v>14649.6</v>
+      </c>
+      <c r="H139">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8">
+      <c r="A140" t="s">
+        <v>21</v>
+      </c>
+      <c r="B140" t="s">
+        <v>179</v>
+      </c>
+      <c r="C140" t="s">
+        <v>220</v>
+      </c>
+      <c r="D140" t="s">
+        <v>356</v>
+      </c>
+      <c r="E140" t="s">
+        <v>510</v>
+      </c>
+      <c r="F140">
+        <v>0</v>
+      </c>
+      <c r="G140">
+        <v>16314.2</v>
+      </c>
+      <c r="H140">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8">
+      <c r="A141" t="s">
+        <v>22</v>
+      </c>
+      <c r="B141" t="s">
+        <v>180</v>
+      </c>
+      <c r="C141" t="s">
+        <v>220</v>
+      </c>
+      <c r="D141" t="s">
+        <v>357</v>
+      </c>
+      <c r="E141" t="s">
+        <v>511</v>
+      </c>
+      <c r="F141">
+        <v>0</v>
+      </c>
+      <c r="G141">
+        <v>5368.3</v>
+      </c>
+      <c r="H141">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8">
+      <c r="A142" t="s">
+        <v>23</v>
+      </c>
+      <c r="B142" t="s">
+        <v>181</v>
+      </c>
+      <c r="C142" t="s">
+        <v>220</v>
+      </c>
+      <c r="D142" t="s">
+        <v>358</v>
+      </c>
+      <c r="E142" t="s">
+        <v>512</v>
+      </c>
+      <c r="F142">
+        <v>0</v>
+      </c>
+      <c r="G142">
+        <v>11112.3</v>
+      </c>
+      <c r="H142">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8">
+      <c r="A143" t="s">
+        <v>24</v>
+      </c>
+      <c r="B143" t="s">
+        <v>182</v>
+      </c>
+      <c r="C143" t="s">
+        <v>221</v>
+      </c>
+      <c r="D143" t="s">
+        <v>359</v>
+      </c>
+      <c r="E143" t="s">
+        <v>513</v>
+      </c>
+      <c r="F143">
+        <v>0</v>
+      </c>
+      <c r="G143">
+        <v>11892.75</v>
+      </c>
+      <c r="H143">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8">
+      <c r="A144" t="s">
+        <v>25</v>
+      </c>
+      <c r="B144" t="s">
+        <v>183</v>
+      </c>
+      <c r="C144" t="s">
+        <v>221</v>
+      </c>
+      <c r="D144" t="s">
+        <v>360</v>
+      </c>
+      <c r="E144" t="s">
+        <v>514</v>
+      </c>
+      <c r="F144">
+        <v>0</v>
+      </c>
+      <c r="G144">
+        <v>9650.75</v>
+      </c>
+      <c r="H144">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8">
+      <c r="A145" t="s">
+        <v>26</v>
+      </c>
+      <c r="B145" t="s">
+        <v>184</v>
+      </c>
+      <c r="C145" t="s">
+        <v>221</v>
+      </c>
+      <c r="D145" t="s">
+        <v>361</v>
+      </c>
+      <c r="E145" t="s">
+        <v>515</v>
+      </c>
+      <c r="F145">
+        <v>0</v>
+      </c>
+      <c r="G145">
+        <v>7976.55</v>
+      </c>
+      <c r="H145">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8">
+      <c r="A146" t="s">
+        <v>27</v>
+      </c>
+      <c r="B146" t="s">
+        <v>185</v>
+      </c>
+      <c r="C146" t="s">
+        <v>209</v>
+      </c>
+      <c r="D146" t="s">
+        <v>362</v>
+      </c>
+      <c r="E146" t="s">
+        <v>516</v>
+      </c>
+      <c r="F146">
+        <v>0</v>
+      </c>
+      <c r="G146">
+        <v>10301.2</v>
+      </c>
+      <c r="H146">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8">
+      <c r="A147" t="s">
+        <v>28</v>
+      </c>
+      <c r="B147" t="s">
+        <v>186</v>
+      </c>
+      <c r="C147" t="s">
+        <v>213</v>
+      </c>
+      <c r="D147" t="s">
+        <v>363</v>
+      </c>
+      <c r="E147" t="s">
+        <v>517</v>
+      </c>
+      <c r="F147">
+        <v>0</v>
+      </c>
+      <c r="G147">
+        <v>10606.15</v>
+      </c>
+      <c r="H147">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8">
+      <c r="A148" t="s">
+        <v>29</v>
+      </c>
+      <c r="B148" t="s">
+        <v>187</v>
+      </c>
+      <c r="C148" t="s">
+        <v>219</v>
+      </c>
+      <c r="D148" t="s">
+        <v>364</v>
+      </c>
+      <c r="E148" t="s">
+        <v>518</v>
+      </c>
+      <c r="F148">
+        <v>0</v>
+      </c>
+      <c r="G148">
+        <v>6130.35</v>
+      </c>
+      <c r="H148">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8">
+      <c r="A149" t="s">
+        <v>30</v>
+      </c>
+      <c r="B149" t="s">
+        <v>188</v>
+      </c>
+      <c r="C149" t="s">
+        <v>221</v>
+      </c>
+      <c r="D149" t="s">
+        <v>365</v>
+      </c>
+      <c r="E149" t="s">
+        <v>519</v>
+      </c>
+      <c r="F149">
+        <v>0</v>
+      </c>
+      <c r="G149">
+        <v>4623.9</v>
+      </c>
+      <c r="H149">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8">
+      <c r="A150" t="s">
+        <v>31</v>
+      </c>
+      <c r="B150" t="s">
+        <v>189</v>
+      </c>
+      <c r="C150" t="s">
+        <v>199</v>
+      </c>
+      <c r="D150" t="s">
+        <v>366</v>
+      </c>
+      <c r="E150" t="s">
+        <v>520</v>
+      </c>
+      <c r="F150">
+        <v>0</v>
+      </c>
+      <c r="G150">
+        <v>5433.4</v>
+      </c>
+      <c r="H150">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8">
+      <c r="A151" t="s">
+        <v>32</v>
+      </c>
+      <c r="B151" t="s">
+        <v>190</v>
+      </c>
+      <c r="C151" t="s">
+        <v>208</v>
+      </c>
+      <c r="D151" t="s">
+        <v>367</v>
+      </c>
+      <c r="E151" t="s">
+        <v>521</v>
+      </c>
+      <c r="F151">
+        <v>0</v>
+      </c>
+      <c r="G151">
+        <v>3751.15</v>
+      </c>
+      <c r="H151">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8">
+      <c r="A152" t="s">
+        <v>33</v>
+      </c>
+      <c r="B152" t="s">
+        <v>191</v>
+      </c>
+      <c r="C152" t="s">
+        <v>199</v>
+      </c>
+      <c r="D152" t="s">
+        <v>368</v>
+      </c>
+      <c r="E152" t="s">
+        <v>522</v>
+      </c>
+      <c r="F152">
+        <v>0</v>
+      </c>
+      <c r="G152">
+        <v>17091.4</v>
+      </c>
+      <c r="H152">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8">
+      <c r="A153" t="s">
+        <v>34</v>
+      </c>
+      <c r="B153" t="s">
+        <v>192</v>
+      </c>
+      <c r="C153" t="s">
+        <v>163</v>
+      </c>
+      <c r="D153" t="s">
+        <v>369</v>
+      </c>
+      <c r="E153" t="s">
+        <v>523</v>
+      </c>
+      <c r="F153">
+        <v>0</v>
+      </c>
+      <c r="G153">
+        <v>1983.1</v>
+      </c>
+      <c r="H153">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8">
+      <c r="A154" t="s">
+        <v>35</v>
+      </c>
+      <c r="B154" t="s">
+        <v>193</v>
+      </c>
+      <c r="C154" t="s">
+        <v>163</v>
+      </c>
+      <c r="D154" t="s">
+        <v>370</v>
+      </c>
+      <c r="E154" t="s">
+        <v>524</v>
+      </c>
+      <c r="F154">
+        <v>0</v>
+      </c>
+      <c r="G154">
+        <v>2949.5</v>
+      </c>
+      <c r="H154">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8">
+      <c r="A155" t="s">
+        <v>36</v>
+      </c>
+      <c r="B155" t="s">
+        <v>194</v>
+      </c>
+      <c r="C155" t="s">
+        <v>80</v>
+      </c>
+      <c r="D155" t="s">
+        <v>371</v>
+      </c>
+      <c r="E155" t="s">
+        <v>525</v>
+      </c>
+      <c r="F155">
+        <v>0</v>
+      </c>
+      <c r="G155">
+        <v>7969.55</v>
+      </c>
+      <c r="H155">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8">
+      <c r="A156" t="s">
+        <v>37</v>
+      </c>
+      <c r="B156" t="s">
+        <v>195</v>
+      </c>
+      <c r="C156" t="s">
+        <v>200</v>
+      </c>
+      <c r="D156" t="s">
+        <v>372</v>
+      </c>
+      <c r="E156" t="s">
+        <v>526</v>
+      </c>
+      <c r="F156">
+        <v>0</v>
+      </c>
+      <c r="G156">
+        <v>2997.8</v>
+      </c>
+      <c r="H156">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8">
+      <c r="A157" t="s">
+        <v>38</v>
+      </c>
+      <c r="B157" t="s">
+        <v>196</v>
+      </c>
+      <c r="C157" t="s">
+        <v>80</v>
+      </c>
+      <c r="D157" t="s">
+        <v>373</v>
+      </c>
+      <c r="E157" t="s">
+        <v>527</v>
+      </c>
+      <c r="F157">
+        <v>0</v>
+      </c>
+      <c r="G157">
+        <v>4571.1</v>
+      </c>
+      <c r="H157">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8">
+      <c r="A158" t="s">
+        <v>39</v>
+      </c>
+      <c r="B158" t="s">
+        <v>197</v>
+      </c>
+      <c r="C158" t="s">
+        <v>210</v>
+      </c>
+      <c r="D158" t="s">
+        <v>374</v>
+      </c>
+      <c r="E158" t="s">
+        <v>528</v>
+      </c>
+      <c r="F158">
+        <v>0</v>
+      </c>
+      <c r="G158">
+        <v>5543.05</v>
+      </c>
+      <c r="H158">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8">
+      <c r="A159" t="s">
+        <v>40</v>
+      </c>
+      <c r="B159" t="s">
+        <v>198</v>
+      </c>
+      <c r="C159" t="s">
+        <v>201</v>
+      </c>
+      <c r="D159" t="s">
+        <v>375</v>
+      </c>
+      <c r="E159" t="s">
+        <v>529</v>
+      </c>
+      <c r="F159">
+        <v>0</v>
+      </c>
+      <c r="G159">
+        <v>2999.6</v>
+      </c>
+      <c r="H159">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1144,1107 +6717,1107 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>12</v>
+        <v>530</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>13</v>
+        <v>531</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>14</v>
+        <v>532</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>15</v>
+        <v>533</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>16</v>
+        <v>534</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>17</v>
+        <v>535</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>18</v>
+        <v>536</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>19</v>
+        <v>537</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>20</v>
+        <v>538</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>21</v>
+        <v>539</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="B2" t="s">
-        <v>22</v>
+        <v>199</v>
       </c>
       <c r="C2" t="s">
-        <v>49</v>
+        <v>551</v>
       </c>
       <c r="D2" t="s">
-        <v>86</v>
+        <v>588</v>
       </c>
       <c r="E2" t="s">
-        <v>123</v>
+        <v>625</v>
       </c>
       <c r="F2" t="s">
-        <v>124</v>
+        <v>626</v>
       </c>
       <c r="G2" t="s">
-        <v>161</v>
+        <v>663</v>
       </c>
       <c r="H2" t="s">
-        <v>198</v>
+        <v>700</v>
       </c>
       <c r="I2" t="s">
-        <v>230</v>
+        <v>700</v>
       </c>
       <c r="J2" t="s">
-        <v>230</v>
+        <v>700</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="B3" t="s">
-        <v>9</v>
+        <v>210</v>
       </c>
       <c r="C3" t="s">
-        <v>50</v>
+        <v>552</v>
       </c>
       <c r="D3" t="s">
-        <v>87</v>
+        <v>589</v>
       </c>
       <c r="E3" t="s">
-        <v>123</v>
+        <v>625</v>
       </c>
       <c r="F3" t="s">
-        <v>125</v>
+        <v>627</v>
       </c>
       <c r="G3" t="s">
-        <v>162</v>
+        <v>664</v>
       </c>
       <c r="H3" t="s">
-        <v>199</v>
+        <v>701</v>
       </c>
       <c r="I3" t="s">
-        <v>231</v>
+        <v>701</v>
       </c>
       <c r="J3" t="s">
-        <v>233</v>
+        <v>701</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="B4" t="s">
-        <v>23</v>
+        <v>80</v>
       </c>
       <c r="C4" t="s">
-        <v>51</v>
+        <v>553</v>
       </c>
       <c r="D4" t="s">
-        <v>88</v>
+        <v>590</v>
       </c>
       <c r="E4" t="s">
-        <v>123</v>
+        <v>625</v>
       </c>
       <c r="F4" t="s">
-        <v>126</v>
+        <v>628</v>
       </c>
       <c r="G4" t="s">
-        <v>163</v>
+        <v>665</v>
       </c>
       <c r="H4" t="s">
-        <v>200</v>
+        <v>702</v>
       </c>
       <c r="I4" t="s">
-        <v>232</v>
+        <v>702</v>
       </c>
       <c r="J4" t="s">
-        <v>232</v>
+        <v>702</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="B5" t="s">
-        <v>24</v>
+        <v>220</v>
       </c>
       <c r="C5" t="s">
-        <v>52</v>
+        <v>554</v>
       </c>
       <c r="D5" t="s">
-        <v>89</v>
+        <v>591</v>
       </c>
       <c r="E5" t="s">
-        <v>123</v>
+        <v>625</v>
       </c>
       <c r="F5" t="s">
-        <v>127</v>
+        <v>629</v>
       </c>
       <c r="G5" t="s">
-        <v>164</v>
+        <v>666</v>
       </c>
       <c r="H5" t="s">
-        <v>201</v>
+        <v>703</v>
       </c>
       <c r="I5" t="s">
-        <v>232</v>
+        <v>703</v>
       </c>
       <c r="J5" t="s">
-        <v>234</v>
+        <v>703</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="B6" t="s">
-        <v>25</v>
+        <v>218</v>
       </c>
       <c r="C6" t="s">
-        <v>53</v>
+        <v>555</v>
       </c>
       <c r="D6" t="s">
-        <v>90</v>
+        <v>592</v>
       </c>
       <c r="E6" t="s">
-        <v>123</v>
+        <v>625</v>
       </c>
       <c r="F6" t="s">
-        <v>128</v>
+        <v>630</v>
       </c>
       <c r="G6" t="s">
-        <v>165</v>
+        <v>667</v>
       </c>
       <c r="H6" t="s">
-        <v>202</v>
+        <v>704</v>
       </c>
       <c r="I6" t="s">
-        <v>232</v>
+        <v>704</v>
       </c>
       <c r="J6" t="s">
-        <v>232</v>
+        <v>704</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="B7" t="s">
-        <v>26</v>
+        <v>208</v>
       </c>
       <c r="C7" t="s">
-        <v>54</v>
+        <v>556</v>
       </c>
       <c r="D7" t="s">
-        <v>91</v>
+        <v>593</v>
       </c>
       <c r="E7" t="s">
-        <v>123</v>
+        <v>625</v>
       </c>
       <c r="F7" t="s">
-        <v>129</v>
+        <v>631</v>
       </c>
       <c r="G7" t="s">
-        <v>166</v>
+        <v>668</v>
       </c>
       <c r="H7" t="s">
-        <v>203</v>
+        <v>705</v>
       </c>
       <c r="I7" t="s">
-        <v>232</v>
+        <v>705</v>
       </c>
       <c r="J7" t="s">
-        <v>232</v>
+        <v>705</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="B8" t="s">
-        <v>27</v>
+        <v>540</v>
       </c>
       <c r="C8" t="s">
-        <v>55</v>
+        <v>557</v>
       </c>
       <c r="D8" t="s">
-        <v>92</v>
+        <v>594</v>
       </c>
       <c r="E8" t="s">
-        <v>123</v>
+        <v>625</v>
       </c>
       <c r="F8" t="s">
-        <v>130</v>
+        <v>632</v>
       </c>
       <c r="G8" t="s">
-        <v>167</v>
+        <v>669</v>
       </c>
       <c r="H8" t="s">
-        <v>204</v>
+        <v>706</v>
       </c>
       <c r="I8" t="s">
-        <v>232</v>
+        <v>706</v>
       </c>
       <c r="J8" t="s">
-        <v>232</v>
+        <v>706</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="B9" t="s">
-        <v>28</v>
+        <v>541</v>
       </c>
       <c r="C9" t="s">
-        <v>56</v>
+        <v>558</v>
       </c>
       <c r="D9" t="s">
-        <v>93</v>
+        <v>595</v>
       </c>
       <c r="E9" t="s">
-        <v>123</v>
+        <v>625</v>
       </c>
       <c r="F9" t="s">
-        <v>131</v>
+        <v>633</v>
       </c>
       <c r="G9" t="s">
-        <v>168</v>
+        <v>670</v>
       </c>
       <c r="H9" t="s">
-        <v>205</v>
+        <v>707</v>
       </c>
       <c r="I9" t="s">
-        <v>232</v>
+        <v>707</v>
       </c>
       <c r="J9" t="s">
-        <v>232</v>
+        <v>707</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="B10" t="s">
-        <v>28</v>
+        <v>541</v>
       </c>
       <c r="C10" t="s">
-        <v>57</v>
+        <v>559</v>
       </c>
       <c r="D10" t="s">
-        <v>94</v>
+        <v>596</v>
       </c>
       <c r="E10" t="s">
-        <v>123</v>
+        <v>625</v>
       </c>
       <c r="F10" t="s">
-        <v>132</v>
+        <v>634</v>
       </c>
       <c r="G10" t="s">
-        <v>169</v>
+        <v>671</v>
       </c>
       <c r="H10" t="s">
-        <v>202</v>
+        <v>704</v>
       </c>
       <c r="I10" t="s">
-        <v>232</v>
+        <v>704</v>
       </c>
       <c r="J10" t="s">
-        <v>232</v>
+        <v>704</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="B11" t="s">
-        <v>29</v>
+        <v>542</v>
       </c>
       <c r="C11" t="s">
-        <v>58</v>
+        <v>560</v>
       </c>
       <c r="D11" t="s">
-        <v>95</v>
+        <v>597</v>
       </c>
       <c r="E11" t="s">
-        <v>123</v>
+        <v>625</v>
       </c>
       <c r="F11" t="s">
-        <v>133</v>
+        <v>635</v>
       </c>
       <c r="G11" t="s">
-        <v>170</v>
+        <v>672</v>
       </c>
       <c r="H11" t="s">
-        <v>206</v>
+        <v>708</v>
       </c>
       <c r="I11" t="s">
-        <v>232</v>
+        <v>708</v>
       </c>
       <c r="J11" t="s">
-        <v>232</v>
+        <v>708</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="B12" t="s">
-        <v>30</v>
+        <v>543</v>
       </c>
       <c r="C12" t="s">
-        <v>59</v>
+        <v>561</v>
       </c>
       <c r="D12" t="s">
-        <v>96</v>
+        <v>598</v>
       </c>
       <c r="E12" t="s">
-        <v>123</v>
+        <v>625</v>
       </c>
       <c r="F12" t="s">
-        <v>134</v>
+        <v>636</v>
       </c>
       <c r="G12" t="s">
-        <v>171</v>
+        <v>673</v>
       </c>
       <c r="H12" t="s">
-        <v>207</v>
+        <v>709</v>
       </c>
       <c r="I12" t="s">
-        <v>232</v>
+        <v>709</v>
       </c>
       <c r="J12" t="s">
-        <v>232</v>
+        <v>709</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="B13" t="s">
-        <v>31</v>
+        <v>544</v>
       </c>
       <c r="C13" t="s">
-        <v>60</v>
+        <v>562</v>
       </c>
       <c r="D13" t="s">
-        <v>97</v>
+        <v>599</v>
       </c>
       <c r="E13" t="s">
-        <v>123</v>
+        <v>625</v>
       </c>
       <c r="F13" t="s">
-        <v>135</v>
+        <v>637</v>
       </c>
       <c r="G13" t="s">
-        <v>172</v>
+        <v>674</v>
       </c>
       <c r="H13" t="s">
-        <v>208</v>
+        <v>710</v>
       </c>
       <c r="I13" t="s">
-        <v>232</v>
+        <v>710</v>
       </c>
       <c r="J13" t="s">
-        <v>232</v>
+        <v>710</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" t="s">
-        <v>32</v>
+        <v>545</v>
       </c>
       <c r="C14" t="s">
-        <v>61</v>
+        <v>563</v>
       </c>
       <c r="D14" t="s">
-        <v>98</v>
+        <v>600</v>
       </c>
       <c r="E14" t="s">
-        <v>123</v>
+        <v>625</v>
       </c>
       <c r="F14" t="s">
-        <v>136</v>
+        <v>638</v>
       </c>
       <c r="G14" t="s">
-        <v>173</v>
+        <v>675</v>
       </c>
       <c r="H14" t="s">
-        <v>209</v>
+        <v>711</v>
       </c>
       <c r="I14" t="s">
-        <v>232</v>
+        <v>711</v>
       </c>
       <c r="J14" t="s">
-        <v>232</v>
+        <v>711</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="B15" t="s">
-        <v>32</v>
+        <v>545</v>
       </c>
       <c r="C15" t="s">
-        <v>62</v>
+        <v>564</v>
       </c>
       <c r="D15" t="s">
-        <v>99</v>
+        <v>601</v>
       </c>
       <c r="E15" t="s">
-        <v>123</v>
+        <v>625</v>
       </c>
       <c r="F15" t="s">
-        <v>137</v>
+        <v>639</v>
       </c>
       <c r="G15" t="s">
-        <v>174</v>
+        <v>676</v>
       </c>
       <c r="H15" t="s">
-        <v>199</v>
+        <v>701</v>
       </c>
       <c r="I15" t="s">
-        <v>232</v>
+        <v>701</v>
       </c>
       <c r="J15" t="s">
-        <v>232</v>
+        <v>701</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="B16" t="s">
-        <v>33</v>
+        <v>546</v>
       </c>
       <c r="C16" t="s">
-        <v>63</v>
+        <v>565</v>
       </c>
       <c r="D16" t="s">
-        <v>100</v>
+        <v>602</v>
       </c>
       <c r="E16" t="s">
-        <v>123</v>
+        <v>625</v>
       </c>
       <c r="F16" t="s">
-        <v>138</v>
+        <v>640</v>
       </c>
       <c r="G16" t="s">
-        <v>175</v>
+        <v>677</v>
       </c>
       <c r="H16" t="s">
-        <v>210</v>
+        <v>712</v>
       </c>
       <c r="I16" t="s">
-        <v>232</v>
+        <v>712</v>
       </c>
       <c r="J16" t="s">
-        <v>232</v>
+        <v>712</v>
       </c>
     </row>
     <row r="17" spans="2:10">
       <c r="B17" t="s">
-        <v>34</v>
+        <v>163</v>
       </c>
       <c r="C17" t="s">
-        <v>64</v>
+        <v>566</v>
       </c>
       <c r="D17" t="s">
-        <v>101</v>
+        <v>603</v>
       </c>
       <c r="E17" t="s">
-        <v>123</v>
+        <v>625</v>
       </c>
       <c r="F17" t="s">
-        <v>139</v>
+        <v>641</v>
       </c>
       <c r="G17" t="s">
-        <v>176</v>
+        <v>678</v>
       </c>
       <c r="H17" t="s">
-        <v>211</v>
+        <v>713</v>
       </c>
       <c r="I17" t="s">
-        <v>232</v>
+        <v>713</v>
       </c>
       <c r="J17" t="s">
-        <v>232</v>
+        <v>713</v>
       </c>
     </row>
     <row r="18" spans="2:10">
       <c r="B18" t="s">
-        <v>35</v>
+        <v>205</v>
       </c>
       <c r="C18" t="s">
-        <v>65</v>
+        <v>567</v>
       </c>
       <c r="D18" t="s">
-        <v>102</v>
+        <v>604</v>
       </c>
       <c r="E18" t="s">
-        <v>123</v>
+        <v>625</v>
       </c>
       <c r="F18" t="s">
-        <v>140</v>
+        <v>642</v>
       </c>
       <c r="G18" t="s">
-        <v>177</v>
+        <v>679</v>
       </c>
       <c r="H18" t="s">
-        <v>212</v>
+        <v>714</v>
       </c>
       <c r="I18" t="s">
-        <v>232</v>
+        <v>714</v>
       </c>
       <c r="J18" t="s">
-        <v>232</v>
+        <v>714</v>
       </c>
     </row>
     <row r="19" spans="2:10">
       <c r="B19" t="s">
-        <v>36</v>
+        <v>547</v>
       </c>
       <c r="C19" t="s">
-        <v>66</v>
+        <v>568</v>
       </c>
       <c r="D19" t="s">
-        <v>103</v>
+        <v>605</v>
       </c>
       <c r="E19" t="s">
-        <v>123</v>
+        <v>625</v>
       </c>
       <c r="F19" t="s">
-        <v>141</v>
+        <v>643</v>
       </c>
       <c r="G19" t="s">
-        <v>178</v>
+        <v>680</v>
       </c>
       <c r="H19" t="s">
-        <v>213</v>
+        <v>715</v>
       </c>
       <c r="I19" t="s">
-        <v>232</v>
+        <v>715</v>
       </c>
       <c r="J19" t="s">
-        <v>232</v>
+        <v>715</v>
       </c>
     </row>
     <row r="20" spans="2:10">
       <c r="B20" t="s">
-        <v>37</v>
+        <v>548</v>
       </c>
       <c r="C20" t="s">
-        <v>67</v>
+        <v>569</v>
       </c>
       <c r="D20" t="s">
-        <v>104</v>
+        <v>606</v>
       </c>
       <c r="E20" t="s">
-        <v>123</v>
+        <v>625</v>
       </c>
       <c r="F20" t="s">
-        <v>142</v>
+        <v>644</v>
       </c>
       <c r="G20" t="s">
-        <v>179</v>
+        <v>681</v>
       </c>
       <c r="H20" t="s">
-        <v>214</v>
+        <v>716</v>
       </c>
       <c r="I20" t="s">
-        <v>232</v>
+        <v>716</v>
       </c>
       <c r="J20" t="s">
-        <v>232</v>
+        <v>716</v>
       </c>
     </row>
     <row r="21" spans="2:10">
       <c r="B21" t="s">
-        <v>38</v>
+        <v>212</v>
       </c>
       <c r="C21" t="s">
-        <v>68</v>
+        <v>570</v>
       </c>
       <c r="D21" t="s">
-        <v>105</v>
+        <v>607</v>
       </c>
       <c r="E21" t="s">
-        <v>123</v>
+        <v>625</v>
       </c>
       <c r="F21" t="s">
-        <v>143</v>
+        <v>645</v>
       </c>
       <c r="G21" t="s">
-        <v>180</v>
+        <v>682</v>
       </c>
       <c r="H21" t="s">
-        <v>215</v>
+        <v>717</v>
       </c>
       <c r="I21" t="s">
-        <v>232</v>
+        <v>717</v>
       </c>
       <c r="J21" t="s">
-        <v>232</v>
+        <v>717</v>
       </c>
     </row>
     <row r="22" spans="2:10">
       <c r="B22" t="s">
-        <v>39</v>
+        <v>549</v>
       </c>
       <c r="C22" t="s">
-        <v>69</v>
+        <v>571</v>
       </c>
       <c r="D22" t="s">
-        <v>106</v>
+        <v>608</v>
       </c>
       <c r="E22" t="s">
-        <v>123</v>
+        <v>625</v>
       </c>
       <c r="F22" t="s">
-        <v>144</v>
+        <v>646</v>
       </c>
       <c r="G22" t="s">
-        <v>181</v>
+        <v>683</v>
       </c>
       <c r="H22" t="s">
-        <v>202</v>
+        <v>704</v>
       </c>
       <c r="I22" t="s">
-        <v>232</v>
+        <v>704</v>
       </c>
       <c r="J22" t="s">
-        <v>232</v>
+        <v>704</v>
       </c>
     </row>
     <row r="23" spans="2:10">
       <c r="B23" t="s">
-        <v>40</v>
+        <v>550</v>
       </c>
       <c r="C23" t="s">
-        <v>70</v>
+        <v>572</v>
       </c>
       <c r="D23" t="s">
-        <v>107</v>
+        <v>609</v>
       </c>
       <c r="E23" t="s">
-        <v>123</v>
+        <v>625</v>
       </c>
       <c r="F23" t="s">
-        <v>145</v>
+        <v>647</v>
       </c>
       <c r="G23" t="s">
-        <v>182</v>
+        <v>684</v>
       </c>
       <c r="H23" t="s">
-        <v>199</v>
+        <v>701</v>
       </c>
       <c r="I23" t="s">
-        <v>232</v>
+        <v>701</v>
       </c>
       <c r="J23" t="s">
-        <v>232</v>
+        <v>701</v>
       </c>
     </row>
     <row r="24" spans="2:10">
       <c r="B24" t="s">
-        <v>40</v>
+        <v>550</v>
       </c>
       <c r="C24" t="s">
-        <v>71</v>
+        <v>573</v>
       </c>
       <c r="D24" t="s">
-        <v>108</v>
+        <v>610</v>
       </c>
       <c r="E24" t="s">
-        <v>123</v>
+        <v>625</v>
       </c>
       <c r="F24" t="s">
-        <v>146</v>
+        <v>648</v>
       </c>
       <c r="G24" t="s">
-        <v>183</v>
+        <v>685</v>
       </c>
       <c r="H24" t="s">
-        <v>216</v>
+        <v>718</v>
       </c>
       <c r="I24" t="s">
-        <v>232</v>
+        <v>718</v>
       </c>
       <c r="J24" t="s">
-        <v>232</v>
+        <v>718</v>
       </c>
     </row>
     <row r="25" spans="2:10">
       <c r="B25" t="s">
-        <v>41</v>
+        <v>216</v>
       </c>
       <c r="C25" t="s">
-        <v>72</v>
+        <v>574</v>
       </c>
       <c r="D25" t="s">
-        <v>109</v>
+        <v>611</v>
       </c>
       <c r="E25" t="s">
-        <v>123</v>
+        <v>625</v>
       </c>
       <c r="F25" t="s">
-        <v>147</v>
+        <v>649</v>
       </c>
       <c r="G25" t="s">
-        <v>184</v>
+        <v>686</v>
       </c>
       <c r="H25" t="s">
-        <v>217</v>
+        <v>719</v>
       </c>
       <c r="I25" t="s">
-        <v>232</v>
+        <v>719</v>
       </c>
       <c r="J25" t="s">
-        <v>232</v>
+        <v>719</v>
       </c>
     </row>
     <row r="26" spans="2:10">
       <c r="B26" t="s">
-        <v>40</v>
+        <v>550</v>
       </c>
       <c r="C26" t="s">
-        <v>73</v>
+        <v>575</v>
       </c>
       <c r="D26" t="s">
-        <v>110</v>
+        <v>612</v>
       </c>
       <c r="E26" t="s">
-        <v>123</v>
+        <v>625</v>
       </c>
       <c r="F26" t="s">
-        <v>148</v>
+        <v>650</v>
       </c>
       <c r="G26" t="s">
-        <v>185</v>
+        <v>687</v>
       </c>
       <c r="H26" t="s">
-        <v>218</v>
+        <v>720</v>
       </c>
       <c r="I26" t="s">
-        <v>232</v>
+        <v>720</v>
       </c>
       <c r="J26" t="s">
-        <v>232</v>
+        <v>720</v>
       </c>
     </row>
     <row r="27" spans="2:10">
       <c r="B27" t="s">
-        <v>42</v>
+        <v>202</v>
       </c>
       <c r="C27" t="s">
-        <v>74</v>
+        <v>576</v>
       </c>
       <c r="D27" t="s">
-        <v>111</v>
+        <v>613</v>
       </c>
       <c r="E27" t="s">
-        <v>123</v>
+        <v>625</v>
       </c>
       <c r="F27" t="s">
-        <v>149</v>
+        <v>651</v>
       </c>
       <c r="G27" t="s">
-        <v>186</v>
+        <v>688</v>
       </c>
       <c r="H27" t="s">
-        <v>219</v>
+        <v>721</v>
       </c>
       <c r="I27" t="s">
-        <v>232</v>
+        <v>721</v>
       </c>
       <c r="J27" t="s">
-        <v>232</v>
+        <v>721</v>
       </c>
     </row>
     <row r="28" spans="2:10">
       <c r="B28" t="s">
-        <v>43</v>
+        <v>221</v>
       </c>
       <c r="C28" t="s">
-        <v>75</v>
+        <v>577</v>
       </c>
       <c r="D28" t="s">
-        <v>112</v>
+        <v>614</v>
       </c>
       <c r="E28" t="s">
-        <v>123</v>
+        <v>625</v>
       </c>
       <c r="F28" t="s">
-        <v>150</v>
+        <v>652</v>
       </c>
       <c r="G28" t="s">
-        <v>187</v>
+        <v>689</v>
       </c>
       <c r="H28" t="s">
-        <v>220</v>
+        <v>722</v>
       </c>
       <c r="I28" t="s">
-        <v>232</v>
+        <v>722</v>
       </c>
       <c r="J28" t="s">
-        <v>232</v>
+        <v>722</v>
       </c>
     </row>
     <row r="29" spans="2:10">
       <c r="B29" t="s">
-        <v>44</v>
+        <v>203</v>
       </c>
       <c r="C29" t="s">
-        <v>76</v>
+        <v>578</v>
       </c>
       <c r="D29" t="s">
-        <v>113</v>
+        <v>615</v>
       </c>
       <c r="E29" t="s">
-        <v>123</v>
+        <v>625</v>
       </c>
       <c r="F29" t="s">
-        <v>151</v>
+        <v>653</v>
       </c>
       <c r="G29" t="s">
-        <v>188</v>
+        <v>690</v>
       </c>
       <c r="H29" t="s">
-        <v>221</v>
+        <v>723</v>
       </c>
       <c r="I29" t="s">
-        <v>232</v>
+        <v>723</v>
       </c>
       <c r="J29" t="s">
-        <v>232</v>
+        <v>723</v>
       </c>
     </row>
     <row r="30" spans="2:10">
       <c r="B30" t="s">
-        <v>45</v>
+        <v>200</v>
       </c>
       <c r="C30" t="s">
-        <v>77</v>
+        <v>579</v>
       </c>
       <c r="D30" t="s">
-        <v>114</v>
+        <v>616</v>
       </c>
       <c r="E30" t="s">
-        <v>123</v>
+        <v>625</v>
       </c>
       <c r="F30" t="s">
-        <v>152</v>
+        <v>654</v>
       </c>
       <c r="G30" t="s">
-        <v>189</v>
+        <v>691</v>
       </c>
       <c r="H30" t="s">
-        <v>222</v>
+        <v>724</v>
       </c>
       <c r="I30" t="s">
-        <v>232</v>
+        <v>724</v>
       </c>
       <c r="J30" t="s">
-        <v>232</v>
+        <v>724</v>
       </c>
     </row>
     <row r="31" spans="2:10">
       <c r="B31" t="s">
-        <v>45</v>
+        <v>200</v>
       </c>
       <c r="C31" t="s">
-        <v>78</v>
+        <v>580</v>
       </c>
       <c r="D31" t="s">
-        <v>115</v>
+        <v>617</v>
       </c>
       <c r="E31" t="s">
-        <v>123</v>
+        <v>625</v>
       </c>
       <c r="F31" t="s">
-        <v>153</v>
+        <v>655</v>
       </c>
       <c r="G31" t="s">
-        <v>190</v>
+        <v>692</v>
       </c>
       <c r="H31" t="s">
-        <v>223</v>
+        <v>725</v>
       </c>
       <c r="I31" t="s">
-        <v>232</v>
+        <v>725</v>
       </c>
       <c r="J31" t="s">
-        <v>232</v>
+        <v>725</v>
       </c>
     </row>
     <row r="32" spans="2:10">
       <c r="B32" t="s">
-        <v>46</v>
+        <v>217</v>
       </c>
       <c r="C32" t="s">
-        <v>79</v>
+        <v>581</v>
       </c>
       <c r="D32" t="s">
-        <v>116</v>
+        <v>618</v>
       </c>
       <c r="E32" t="s">
-        <v>123</v>
+        <v>625</v>
       </c>
       <c r="F32" t="s">
-        <v>154</v>
+        <v>656</v>
       </c>
       <c r="G32" t="s">
-        <v>191</v>
+        <v>693</v>
       </c>
       <c r="H32" t="s">
-        <v>224</v>
+        <v>726</v>
       </c>
       <c r="I32" t="s">
-        <v>232</v>
+        <v>726</v>
       </c>
       <c r="J32" t="s">
-        <v>232</v>
+        <v>726</v>
       </c>
     </row>
     <row r="33" spans="2:10">
       <c r="B33" t="s">
-        <v>47</v>
+        <v>209</v>
       </c>
       <c r="C33" t="s">
-        <v>80</v>
+        <v>582</v>
       </c>
       <c r="D33" t="s">
-        <v>117</v>
+        <v>619</v>
       </c>
       <c r="E33" t="s">
-        <v>123</v>
+        <v>625</v>
       </c>
       <c r="F33" t="s">
-        <v>155</v>
+        <v>657</v>
       </c>
       <c r="G33" t="s">
-        <v>192</v>
+        <v>694</v>
       </c>
       <c r="H33" t="s">
-        <v>225</v>
+        <v>727</v>
       </c>
       <c r="I33" t="s">
-        <v>232</v>
+        <v>727</v>
       </c>
       <c r="J33" t="s">
-        <v>232</v>
+        <v>727</v>
       </c>
     </row>
     <row r="34" spans="2:10">
       <c r="B34" t="s">
-        <v>47</v>
+        <v>209</v>
       </c>
       <c r="C34" t="s">
-        <v>81</v>
+        <v>583</v>
       </c>
       <c r="D34" t="s">
-        <v>118</v>
+        <v>620</v>
       </c>
       <c r="E34" t="s">
-        <v>123</v>
+        <v>625</v>
       </c>
       <c r="F34" t="s">
-        <v>156</v>
+        <v>658</v>
       </c>
       <c r="G34" t="s">
-        <v>193</v>
+        <v>695</v>
       </c>
       <c r="H34" t="s">
-        <v>203</v>
+        <v>705</v>
       </c>
       <c r="I34" t="s">
-        <v>232</v>
+        <v>705</v>
       </c>
       <c r="J34" t="s">
-        <v>232</v>
+        <v>705</v>
       </c>
     </row>
     <row r="35" spans="2:10">
       <c r="B35" t="s">
-        <v>48</v>
+        <v>214</v>
       </c>
       <c r="C35" t="s">
-        <v>82</v>
+        <v>584</v>
       </c>
       <c r="D35" t="s">
-        <v>119</v>
+        <v>621</v>
       </c>
       <c r="E35" t="s">
-        <v>123</v>
+        <v>625</v>
       </c>
       <c r="F35" t="s">
-        <v>157</v>
+        <v>659</v>
       </c>
       <c r="G35" t="s">
-        <v>194</v>
+        <v>696</v>
       </c>
       <c r="H35" t="s">
-        <v>226</v>
+        <v>728</v>
       </c>
       <c r="I35" t="s">
-        <v>232</v>
+        <v>728</v>
       </c>
       <c r="J35" t="s">
-        <v>232</v>
+        <v>728</v>
       </c>
     </row>
     <row r="36" spans="2:10">
       <c r="B36" t="s">
-        <v>48</v>
+        <v>214</v>
       </c>
       <c r="C36" t="s">
-        <v>83</v>
+        <v>585</v>
       </c>
       <c r="D36" t="s">
-        <v>120</v>
+        <v>622</v>
       </c>
       <c r="E36" t="s">
-        <v>123</v>
+        <v>625</v>
       </c>
       <c r="F36" t="s">
-        <v>158</v>
+        <v>660</v>
       </c>
       <c r="G36" t="s">
-        <v>195</v>
+        <v>697</v>
       </c>
       <c r="H36" t="s">
-        <v>227</v>
+        <v>729</v>
       </c>
       <c r="I36" t="s">
-        <v>232</v>
+        <v>729</v>
       </c>
       <c r="J36" t="s">
-        <v>232</v>
+        <v>729</v>
       </c>
     </row>
     <row r="37" spans="2:10">
       <c r="B37" t="s">
-        <v>48</v>
+        <v>214</v>
       </c>
       <c r="C37" t="s">
-        <v>84</v>
+        <v>586</v>
       </c>
       <c r="D37" t="s">
-        <v>121</v>
+        <v>623</v>
       </c>
       <c r="E37" t="s">
-        <v>123</v>
+        <v>625</v>
       </c>
       <c r="F37" t="s">
-        <v>159</v>
+        <v>661</v>
       </c>
       <c r="G37" t="s">
-        <v>196</v>
+        <v>698</v>
       </c>
       <c r="H37" t="s">
-        <v>228</v>
+        <v>730</v>
       </c>
       <c r="I37" t="s">
-        <v>232</v>
+        <v>730</v>
       </c>
       <c r="J37" t="s">
-        <v>232</v>
+        <v>730</v>
       </c>
     </row>
     <row r="38" spans="2:10">
       <c r="B38" t="s">
-        <v>48</v>
+        <v>214</v>
       </c>
       <c r="C38" t="s">
-        <v>85</v>
+        <v>587</v>
       </c>
       <c r="D38" t="s">
-        <v>122</v>
+        <v>624</v>
       </c>
       <c r="E38" t="s">
-        <v>123</v>
+        <v>625</v>
       </c>
       <c r="F38" t="s">
-        <v>160</v>
+        <v>662</v>
       </c>
       <c r="G38" t="s">
-        <v>197</v>
+        <v>699</v>
       </c>
       <c r="H38" t="s">
-        <v>229</v>
+        <v>731</v>
       </c>
       <c r="I38" t="s">
-        <v>232</v>
+        <v>731</v>
       </c>
       <c r="J38" t="s">
-        <v>232</v>
+        <v>731</v>
       </c>
     </row>
   </sheetData>
